--- a/GREENBANK0_301A/project/Sanity.xlsx
+++ b/GREENBANK0_301A/project/Sanity.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="682">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -175,7 +175,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -1551,6 +1554,9 @@
   </si>
   <si>
     <t>amux2</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -2470,47 +2476,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2520,52 +2526,52 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2580,7 +2586,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2600,7 +2606,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2615,7 +2621,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2630,7 +2636,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2650,12 +2656,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2670,212 +2676,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2890,12 +2896,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2910,7 +2916,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2930,127 +2936,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3065,7 +3071,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3330,17 +3336,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3355,7 +3361,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3375,17 +3381,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3400,52 +3406,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3460,81 +3466,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" t="s">
         <v>193</v>
-      </c>
-      <c r="B6" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" t="s">
         <v>196</v>
-      </c>
-      <c r="B8" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" t="s">
         <v>201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3542,185 +3548,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3728,453 +3734,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B79" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B83" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B92" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B95" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B97" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B98" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B100" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -4182,628 +4188,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B106" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B109" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B112" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B113" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B116" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B117" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B118" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B121" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B122" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B123" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B124" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B125" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B126" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B127" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B128" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B129" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B131" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B132" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B133" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B134" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B135" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B136" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B137" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B138" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B139" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B140" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B141" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B142" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B143" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B144" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B145" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B146" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B147" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B148" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B149" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B150" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B151" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B153" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B154" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B156" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B157" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B160" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B161" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B162" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B163" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B164" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B165" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B166" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B167" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B168" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B169" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B170" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B171" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B172" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B173" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B174" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B175" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B176" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B177" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B178" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B179" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B180" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4818,47 +4824,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4866,15 +4872,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4882,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -4897,246 +4903,246 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F5" t="s">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" t="s">
         <v>445</v>
       </c>
-      <c r="C6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D6" t="s">
-        <v>444</v>
-      </c>
       <c r="E6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F6" t="s">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F7" t="s">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F8" t="s">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F9" t="s">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F10" t="s">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F11" t="s">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F12" t="s">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F13" t="s">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F14" t="s">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="B15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E15" t="s">
         <v>1</v>
@@ -5145,18 +5151,18 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C16" t="s">
+        <v>459</v>
+      </c>
+      <c r="D16" t="s">
         <v>458</v>
-      </c>
-      <c r="D16" t="s">
-        <v>457</v>
       </c>
       <c r="E16" t="s">
         <v>1</v>
@@ -5165,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -5180,26 +5186,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5209,12 +5215,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5224,226 +5230,234 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B24" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B27" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B30" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B31" t="s">
-        <v>433</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>498</v>
+      </c>
+      <c r="B32" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -5458,1164 +5472,1164 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B5" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E5" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G5" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J5" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B6" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C6" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H6" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J6" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K6" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C7" t="s">
+        <v>524</v>
+      </c>
+      <c r="D7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7" t="s">
+        <v>514</v>
+      </c>
+      <c r="F7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" t="s">
+        <v>514</v>
+      </c>
+      <c r="H7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I7" t="s">
+        <v>525</v>
+      </c>
+      <c r="J7" t="s">
+        <v>517</v>
+      </c>
+      <c r="K7" t="s">
         <v>522</v>
-      </c>
-      <c r="D7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E7" t="s">
-        <v>512</v>
-      </c>
-      <c r="F7" t="s">
-        <v>226</v>
-      </c>
-      <c r="G7" t="s">
-        <v>512</v>
-      </c>
-      <c r="H7" t="s">
-        <v>513</v>
-      </c>
-      <c r="I7" t="s">
-        <v>523</v>
-      </c>
-      <c r="J7" t="s">
-        <v>515</v>
-      </c>
-      <c r="K7" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C9" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B11" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C11" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>529</v>
+      </c>
+      <c r="B13" t="s">
         <v>527</v>
       </c>
-      <c r="B13" t="s">
-        <v>525</v>
-      </c>
       <c r="C13" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B14" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C14" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>530</v>
+      </c>
+      <c r="B15" t="s">
+        <v>527</v>
+      </c>
+      <c r="C15" t="s">
         <v>528</v>
       </c>
-      <c r="B15" t="s">
-        <v>525</v>
-      </c>
-      <c r="C15" t="s">
-        <v>526</v>
-      </c>
       <c r="D15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B16" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C16" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E16" t="s">
+        <v>514</v>
+      </c>
+      <c r="F16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G16" t="s">
         <v>512</v>
       </c>
-      <c r="F16" t="s">
-        <v>266</v>
-      </c>
-      <c r="G16" t="s">
-        <v>510</v>
-      </c>
       <c r="H16" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I16" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J16" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K16" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B17" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C17" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E17" t="s">
+        <v>514</v>
+      </c>
+      <c r="F17" t="s">
+        <v>267</v>
+      </c>
+      <c r="G17" t="s">
         <v>512</v>
       </c>
-      <c r="F17" t="s">
-        <v>266</v>
-      </c>
-      <c r="G17" t="s">
-        <v>510</v>
-      </c>
       <c r="H17" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I17" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J17" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K17" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B18" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C18" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E18" t="s">
+        <v>514</v>
+      </c>
+      <c r="F18" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" t="s">
         <v>512</v>
       </c>
-      <c r="F18" t="s">
-        <v>266</v>
-      </c>
-      <c r="G18" t="s">
-        <v>510</v>
-      </c>
       <c r="H18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I18" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J18" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K18" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B19" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C19" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E19" t="s">
+        <v>514</v>
+      </c>
+      <c r="F19" t="s">
+        <v>267</v>
+      </c>
+      <c r="G19" t="s">
         <v>512</v>
       </c>
-      <c r="F19" t="s">
-        <v>266</v>
-      </c>
-      <c r="G19" t="s">
-        <v>510</v>
-      </c>
       <c r="H19" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I19" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J19" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K19" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B20" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C20" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K20" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B21" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C21" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B22" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C22" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K22" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B23" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C23" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E23" t="s">
+        <v>514</v>
+      </c>
+      <c r="F23" t="s">
+        <v>267</v>
+      </c>
+      <c r="G23" t="s">
         <v>512</v>
       </c>
-      <c r="F23" t="s">
-        <v>266</v>
-      </c>
-      <c r="G23" t="s">
-        <v>510</v>
-      </c>
       <c r="H23" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I23" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J23" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K23" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B24" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C24" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E24" t="s">
+        <v>514</v>
+      </c>
+      <c r="F24" t="s">
+        <v>267</v>
+      </c>
+      <c r="G24" t="s">
         <v>512</v>
       </c>
-      <c r="F24" t="s">
-        <v>266</v>
-      </c>
-      <c r="G24" t="s">
-        <v>510</v>
-      </c>
       <c r="H24" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I24" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J24" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K24" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B25" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C25" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E25" t="s">
+        <v>514</v>
+      </c>
+      <c r="F25" t="s">
+        <v>267</v>
+      </c>
+      <c r="G25" t="s">
         <v>512</v>
       </c>
-      <c r="F25" t="s">
-        <v>266</v>
-      </c>
-      <c r="G25" t="s">
-        <v>510</v>
-      </c>
       <c r="H25" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I25" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J25" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K25" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B26" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C26" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E26" t="s">
+        <v>514</v>
+      </c>
+      <c r="F26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G26" t="s">
         <v>512</v>
       </c>
-      <c r="F26" t="s">
-        <v>266</v>
-      </c>
-      <c r="G26" t="s">
-        <v>510</v>
-      </c>
       <c r="H26" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I26" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J26" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K26" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E27" t="s">
+        <v>514</v>
+      </c>
+      <c r="F27" t="s">
+        <v>267</v>
+      </c>
+      <c r="G27" t="s">
         <v>512</v>
       </c>
-      <c r="F27" t="s">
-        <v>266</v>
-      </c>
-      <c r="G27" t="s">
-        <v>510</v>
-      </c>
       <c r="H27" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I27" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J27" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B28" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C28" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B29" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C29" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E29" t="s">
+        <v>514</v>
+      </c>
+      <c r="F29" t="s">
+        <v>267</v>
+      </c>
+      <c r="G29" t="s">
         <v>512</v>
       </c>
-      <c r="F29" t="s">
-        <v>266</v>
-      </c>
-      <c r="G29" t="s">
-        <v>510</v>
-      </c>
       <c r="H29" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I29" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J29" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K29" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B30" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C30" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" t="s">
+        <v>514</v>
+      </c>
+      <c r="F30" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" t="s">
         <v>512</v>
       </c>
-      <c r="F30" t="s">
-        <v>266</v>
-      </c>
-      <c r="G30" t="s">
-        <v>510</v>
-      </c>
       <c r="H30" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I30" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J30" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K30" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E31" t="s">
+        <v>514</v>
+      </c>
+      <c r="F31" t="s">
+        <v>267</v>
+      </c>
+      <c r="G31" t="s">
         <v>512</v>
       </c>
-      <c r="F31" t="s">
-        <v>266</v>
-      </c>
-      <c r="G31" t="s">
-        <v>510</v>
-      </c>
       <c r="H31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B32" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C32" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E32" t="s">
+        <v>514</v>
+      </c>
+      <c r="F32" t="s">
+        <v>267</v>
+      </c>
+      <c r="G32" t="s">
         <v>512</v>
       </c>
-      <c r="F32" t="s">
-        <v>266</v>
-      </c>
-      <c r="G32" t="s">
-        <v>510</v>
-      </c>
       <c r="H32" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I32" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J32" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K32" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B33" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C33" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E33" t="s">
+        <v>514</v>
+      </c>
+      <c r="F33" t="s">
+        <v>267</v>
+      </c>
+      <c r="G33" t="s">
         <v>512</v>
       </c>
-      <c r="F33" t="s">
-        <v>266</v>
-      </c>
-      <c r="G33" t="s">
-        <v>510</v>
-      </c>
       <c r="H33" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I33" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J33" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K33" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B34" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C34" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E34" t="s">
+        <v>514</v>
+      </c>
+      <c r="F34" t="s">
+        <v>267</v>
+      </c>
+      <c r="G34" t="s">
         <v>512</v>
       </c>
-      <c r="F34" t="s">
-        <v>266</v>
-      </c>
-      <c r="G34" t="s">
-        <v>510</v>
-      </c>
       <c r="H34" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I34" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J34" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K34" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B35" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C35" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E35" t="s">
+        <v>514</v>
+      </c>
+      <c r="F35" t="s">
+        <v>267</v>
+      </c>
+      <c r="G35" t="s">
         <v>512</v>
       </c>
-      <c r="F35" t="s">
-        <v>266</v>
-      </c>
-      <c r="G35" t="s">
-        <v>510</v>
-      </c>
       <c r="H35" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I35" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J35" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K35" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C36" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K36" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -6625,7 +6639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6641,6 +6655,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -6655,7 +6674,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6665,94 +6684,94 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B5" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F5" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" t="s">
+        <v>458</v>
+      </c>
+      <c r="F6" t="s">
         <v>588</v>
       </c>
-      <c r="C6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E6" t="s">
-        <v>457</v>
-      </c>
-      <c r="F6" t="s">
-        <v>586</v>
-      </c>
       <c r="G6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B7" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F7" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G7" t="s">
         <v>1</v>
@@ -6760,285 +6779,285 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B9" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H9" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B10" t="s">
+        <v>598</v>
+      </c>
+      <c r="C10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D10" t="s">
+        <v>334</v>
+      </c>
+      <c r="E10" t="s">
         <v>445</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>596</v>
       </c>
-      <c r="C10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D10" t="s">
-        <v>333</v>
-      </c>
-      <c r="E10" t="s">
-        <v>444</v>
-      </c>
-      <c r="F10" t="s">
-        <v>594</v>
-      </c>
       <c r="G10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H10" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B11" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F11" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H11" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B12" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F12" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H12" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F13" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H13" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F14" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H14" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B15" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F15" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H15" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B16" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E16" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F16" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H16" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B17" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D17" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E17" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F17" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H17" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B18" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E18" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F18" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H18" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -7053,7 +7072,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7063,288 +7082,288 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D5" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G5" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H5" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" t="s">
+        <v>596</v>
+      </c>
+      <c r="E6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" t="s">
         <v>445</v>
       </c>
-      <c r="B6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D6" t="s">
-        <v>594</v>
-      </c>
-      <c r="E6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" t="s">
-        <v>444</v>
-      </c>
       <c r="G6" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H6" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D7" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G7" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G8" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D9" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G9" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H9" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D10" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G10" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H10" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D11" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G11" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H11" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G12" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H12" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D13" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G13" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H13" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D14" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G14" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H14" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -7359,44 +7378,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -7411,44 +7430,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -7463,22 +7482,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -7493,22 +7512,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -7523,7 +7542,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -7538,12 +7557,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7553,12 +7572,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -7573,7 +7592,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -7588,7 +7607,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -7603,7 +7622,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7613,57 +7632,57 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7673,7 +7692,7 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -7683,7 +7702,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -7693,57 +7712,57 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -7758,12 +7777,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7773,7 +7792,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -7788,12 +7807,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -7808,12 +7827,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -7828,7 +7847,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7843,127 +7862,127 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -7978,7 +7997,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7988,7 +8007,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -8003,7 +8022,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8013,7 +8032,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -8028,7 +8047,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8038,47 +8057,47 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -8088,52 +8107,52 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -8148,37 +8167,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -8193,37 +8212,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Sanity.xlsx
+++ b/GREENBANK0_301A/project/Sanity.xlsx
@@ -32,31 +32,30 @@
     <sheet name="Project Summary" sheetId="23" r:id="rId23"/>
     <sheet name="Design Params and Codes" sheetId="24" r:id="rId24"/>
     <sheet name="DRM Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Register Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="DFT Summary" sheetId="27" r:id="rId27"/>
-    <sheet name="Nesto Usage Report" sheetId="28" r:id="rId28"/>
-    <sheet name="PAD REPORT" sheetId="29" r:id="rId29"/>
-    <sheet name="REGISTER ADDRESS REPORT" sheetId="30" r:id="rId30"/>
-    <sheet name="REGISTER DETAIL ADDRESS REPORT" sheetId="31" r:id="rId31"/>
-    <sheet name="FACTORY ADDRESS REPORT" sheetId="32" r:id="rId32"/>
-    <sheet name="ACCURACY ADDRESS REPORT" sheetId="33" r:id="rId33"/>
-    <sheet name="DFT PROBE ADDRESS REPORT" sheetId="34" r:id="rId34"/>
-    <sheet name="DFT HIJACK ADDRESS REPORT" sheetId="35" r:id="rId35"/>
-    <sheet name="DFT DBUF ADDRESS REPORT" sheetId="36" r:id="rId36"/>
-    <sheet name="TMA SUMMARY REPORT (DFTs)" sheetId="37" r:id="rId37"/>
-    <sheet name="DFT CELL GLOBAL ADDRESS REPORT" sheetId="38" r:id="rId38"/>
-    <sheet name="DFT CELL DBUF ADDRESS REPORT" sheetId="39" r:id="rId39"/>
-    <sheet name="DFT CELL ADDRESS REPORT (Rich)" sheetId="40" r:id="rId40"/>
-    <sheet name="DFT dftprobe Checker" sheetId="41" r:id="rId41"/>
-    <sheet name="DFT dfthijack Checker" sheetId="42" r:id="rId42"/>
-    <sheet name="Pad Checker" sheetId="43" r:id="rId43"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="PAD REPORT" sheetId="28" r:id="rId28"/>
+    <sheet name="REGISTER ADDRESS REPORT" sheetId="29" r:id="rId29"/>
+    <sheet name="REGISTER DETAIL ADDRESS REPORT" sheetId="30" r:id="rId30"/>
+    <sheet name="FACTORY ADDRESS REPORT" sheetId="31" r:id="rId31"/>
+    <sheet name="ACCURACY ADDRESS REPORT" sheetId="32" r:id="rId32"/>
+    <sheet name="DFT PROBE ADDRESS REPORT" sheetId="33" r:id="rId33"/>
+    <sheet name="DFT HIJACK ADDRESS REPORT" sheetId="34" r:id="rId34"/>
+    <sheet name="DFT DBUF ADDRESS REPORT" sheetId="35" r:id="rId35"/>
+    <sheet name="TMA SUMMARY REPORT (DFTs)" sheetId="36" r:id="rId36"/>
+    <sheet name="DFT CELL GLOBAL ADDRESS REPORT" sheetId="37" r:id="rId37"/>
+    <sheet name="DFT CELL DBUF ADDRESS REPORT" sheetId="38" r:id="rId38"/>
+    <sheet name="DFT CELL ADDRESS REPORT (Rich)" sheetId="39" r:id="rId39"/>
+    <sheet name="DFT dftprobe Checker" sheetId="40" r:id="rId40"/>
+    <sheet name="DFT dfthijack Checker" sheetId="41" r:id="rId41"/>
+    <sheet name="Pad Checker" sheetId="42" r:id="rId42"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="598">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -175,175 +174,103 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+    <t>All symbols have nets.</t>
+  </si>
+  <si>
+    <t>Shorted Inputs</t>
+  </si>
+  <si>
+    <t>No Shorted Input Nets found.</t>
+  </si>
+  <si>
+    <t>Shorted Outputs</t>
+  </si>
+  <si>
+    <t>No Shorted Output Nets found.</t>
+  </si>
+  <si>
+    <t>Floating Inputs</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XU1</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.scli(scli)</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
+  </si>
+  <si>
+    <t>No Connects - Outputs</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE</t>
+  </si>
+  <si>
+    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>No Connects - Inputs</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
   </si>
   <si>
-    <t>XU9,SIMPV</t>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
   </si>
   <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPFIXEDlow</t>
-  </si>
-  <si>
-    <t>XU1,SIMPV</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPFIXEDmedium</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENhigh</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENlow</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENmedium</t>
-  </si>
-  <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
-  </si>
-  <si>
-    <t>Floating Inputs</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(30)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(29)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(28)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOCONFIGURE1.enable_ldo(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOFIXED.enable_ldo(114)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOSTANDALONE.enable_ldo(116)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOUNITY.enable_ldo(119)</t>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>XU1,XceleraRING</t>
   </si>
   <si>
-    <t>Floating pin XCELINA.ten_taext(ten_taext)</t>
-  </si>
-  <si>
-    <t>Floating pin XCELIND.ten_tdext(ten_tdext)</t>
-  </si>
-  <si>
-    <t>XU1</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.scli(scli)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE</t>
-  </si>
-  <si>
-    <t>Floating pin XSERVICE.CELBG83021(CELBG83021)</t>
-  </si>
-  <si>
-    <t>Floating pin XCELIND.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XU1,XceleraRING,XCELIND", "instance": "XCELIND", "symbol": "tdext", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_tdext - {"path": "XU1,XceleraRING,XCELIND", "instance": "XCELIND", "symbol": "ten_tdext", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
@@ -788,7 +715,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/sim_GREENBANK_301A.net</t>
+    <t>/tmp/kyle/mnt/celera/projects/Simplis/playrelease/Release/play301a/Regression/SIMPLIS_Data/sim_GREENBANK_301A.net</t>
   </si>
   <si>
     <t>gen_reports</t>
@@ -1379,453 +1306,393 @@
     <t>61</t>
   </si>
   <si>
-    <t>Register Summary</t>
+    <t>DFT Summary</t>
   </si>
   <si>
     <t>TMA</t>
   </si>
   <si>
+    <t>Nesto Usage Report</t>
+  </si>
+  <si>
+    <t>Nesto</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>pinprobe</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>switchgnd</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>amplifier</t>
+  </si>
+  <si>
+    <t>IPOTTldo</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>nor3</t>
+  </si>
+  <si>
+    <t>ESDminiClamp6</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>currentgenerator</t>
+  </si>
+  <si>
+    <t>celeranoconn</t>
+  </si>
+  <si>
+    <t>switchtransmission</t>
+  </si>
+  <si>
+    <t>porb</t>
+  </si>
+  <si>
+    <t>oscillatorcrude</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>decoder3</t>
+  </si>
+  <si>
+    <t>amux8</t>
+  </si>
+  <si>
+    <t>amux2</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
+  </si>
+  <si>
+    <t>PAD REPORT</t>
+  </si>
+  <si>
+    <t>Package TQFN3255</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Abs Min</t>
+  </si>
+  <si>
+    <t>Wrt Min</t>
+  </si>
+  <si>
+    <t>Abs Max</t>
+  </si>
+  <si>
+    <t>Wrt Max</t>
+  </si>
+  <si>
+    <t>ESD Rating</t>
+  </si>
+  <si>
+    <t>ESD Connect</t>
+  </si>
+  <si>
+    <t>Imax</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>MUDV</t>
+  </si>
+  <si>
+    <t>Supply</t>
+  </si>
+  <si>
+    <t>MUDG</t>
+  </si>
+  <si>
+    <t>2KV</t>
+  </si>
+  <si>
+    <t>ESDcore6 MUDV -&gt; GESD &amp; ESDcore6 CELPOWER_LDO -&gt; GESD</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>CELINA</t>
+  </si>
+  <si>
+    <t>DFT analog input testmode pad (Connect to GND)</t>
+  </si>
+  <si>
+    <t>ESDcore6 CELINA -&gt; GESD</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>No Connect</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>LDO15</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO15 &amp; ESDdiode LDO15 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>LDO14</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO14 &amp; ESDdiode LDO14 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>LDO13</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO13 &amp; ESDdiode LDO13 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>LDO12</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO12 &amp; ESDdiode LDO12 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>LDO11</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO11 &amp; ESDdiode LDO11 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>LDO10</t>
+  </si>
+  <si>
+    <t>Data1</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO10 &amp; ESDdiode LDO10 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>LDO9</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO9 &amp; ESDdiode LDO9 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>LDO8</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO8 &amp; ESDdiode LDO8 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>LDO7</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO7 &amp; ESDdiode LDO7 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>LDO6</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO6 &amp; ESDdiode LDO6 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>LDO5</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO5 &amp; ESDdiode LDO5 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>LDO4</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO4 &amp; ESDdiode LDO4 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>LDO3</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO3 &amp; ESDdiode LDO3 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>LDO2</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO2 &amp; ESDdiode LDO2 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>LDO1</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO1 &amp; ESDdiode LDO1 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>LDO0</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO0 &amp; ESDdiode LDO0 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>REGISTER ADDRESS REPORT</t>
+  </si>
+  <si>
+    <t>Slave</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>r/w</t>
+  </si>
+  <si>
     <t>Bits</t>
   </si>
   <si>
-    <t>Start</t>
-  </si>
-  <si>
     <t>POR</t>
   </si>
   <si>
-    <t>AMPCONTROLHIGHgain</t>
-  </si>
-  <si>
-    <t>rw</t>
-  </si>
-  <si>
-    <t>AMPCONTROLMEDIUMgain</t>
-  </si>
-  <si>
-    <t>AMPCONTROLSLOWgain</t>
-  </si>
-  <si>
-    <t>AMPLIFIERconfiguration</t>
-  </si>
-  <si>
-    <t>LDOconfigurationA</t>
-  </si>
-  <si>
-    <t>REF2output</t>
-  </si>
-  <si>
-    <t>REF3output</t>
-  </si>
-  <si>
-    <t>REFERENCEselect</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>SERVICEconfiguration</t>
-  </si>
-  <si>
-    <t>0x21</t>
-  </si>
-  <si>
-    <t>XU2</t>
-  </si>
-  <si>
-    <t>0x22</t>
+    <t>CHIPIDLSB</t>
+  </si>
+  <si>
+    <t>ChipID LSB</t>
   </si>
   <si>
     <t>ro</t>
   </si>
   <si>
-    <t>0x23</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>Nesto Usage Report</t>
-  </si>
-  <si>
-    <t>Nesto</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>pinprobe</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>switchgnd</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>amplifier</t>
-  </si>
-  <si>
-    <t>IPOTTldo</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
-    <t>capacitorfixed</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
-    <t>nor3</t>
-  </si>
-  <si>
-    <t>ESDminiClamp6</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>currentgenerator</t>
-  </si>
-  <si>
-    <t>celeranoconn</t>
-  </si>
-  <si>
-    <t>switchtransmission</t>
-  </si>
-  <si>
-    <t>porb</t>
-  </si>
-  <si>
-    <t>oscillatorcrude</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>decoder3</t>
-  </si>
-  <si>
-    <t>amux8</t>
-  </si>
-  <si>
-    <t>amux2</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
-  </si>
-  <si>
-    <t>PAD REPORT</t>
-  </si>
-  <si>
-    <t>Package TQFN3255</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Abs Min</t>
-  </si>
-  <si>
-    <t>Wrt Min</t>
-  </si>
-  <si>
-    <t>Abs Max</t>
-  </si>
-  <si>
-    <t>Wrt Max</t>
-  </si>
-  <si>
-    <t>ESD Rating</t>
-  </si>
-  <si>
-    <t>ESD Connect</t>
-  </si>
-  <si>
-    <t>Imax</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>MUDV</t>
-  </si>
-  <si>
-    <t>Supply</t>
-  </si>
-  <si>
-    <t>MUDG</t>
-  </si>
-  <si>
-    <t>2KV</t>
-  </si>
-  <si>
-    <t>ESDcore6 MUDV -&gt; GESD &amp; ESDcore6 CELPOWER_LDO -&gt; GESD</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>CELINA</t>
-  </si>
-  <si>
-    <t>DFT analog input testmode pad (Connect to GND)</t>
-  </si>
-  <si>
-    <t>ESDcore6 CELINA -&gt; GESD</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>CELIND</t>
-  </si>
-  <si>
-    <t>DFT digital input testmode pad (Connect to GND)</t>
-  </si>
-  <si>
-    <t>ESDcore6 CELIND -&gt; GESD</t>
-  </si>
-  <si>
-    <t>Ground</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>No Connect</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>LDO15</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO15 &amp; ESDdiode LDO15 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>LDO14</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO14 &amp; ESDdiode LDO14 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>LDO13</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO13 &amp; ESDdiode LDO13 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>LDO12</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO12 &amp; ESDdiode LDO12 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>LDO11</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO11 &amp; ESDdiode LDO11 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>LDO10</t>
-  </si>
-  <si>
-    <t>Data1</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO10 &amp; ESDdiode LDO10 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>LDO9</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO9 &amp; ESDdiode LDO9 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>LDO8</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO8 &amp; ESDdiode LDO8 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>LDO7</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO7 &amp; ESDdiode LDO7 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>LDO6</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO6 &amp; ESDdiode LDO6 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>LDO5</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO5 &amp; ESDdiode LDO5 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>LDO4</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO4 &amp; ESDdiode LDO4 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>LDO3</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO3 &amp; ESDdiode LDO3 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>LDO2</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO2 &amp; ESDdiode LDO2 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>LDO1</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO1 &amp; ESDdiode LDO1 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>LDO0</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO0 &amp; ESDdiode LDO0 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>REGISTER ADDRESS REPORT</t>
-  </si>
-  <si>
-    <t>Slave</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>r/w</t>
-  </si>
-  <si>
-    <t>CHIPIDLSB</t>
-  </si>
-  <si>
-    <t>ChipID LSB</t>
-  </si>
-  <si>
     <t>7:0</t>
   </si>
   <si>
@@ -1847,72 +1714,6 @@
     <t>Factory ID</t>
   </si>
   <si>
-    <t>AMP CONTROL High gain adjustment</t>
-  </si>
-  <si>
-    <t>2:0</t>
-  </si>
-  <si>
-    <t>XU1,XU20,XAMPCONTROLhigh,Xdatamap1</t>
-  </si>
-  <si>
-    <t>AMP CONTROL Medium gain adjustment</t>
-  </si>
-  <si>
-    <t>XU1,XU20,XAMPCONTROLmedium,Xdatamap1</t>
-  </si>
-  <si>
-    <t>AMP CONTROL Slow gain adjustment</t>
-  </si>
-  <si>
-    <t>XU1,XU20,XAMPCONTROLlow,Xdatamap1</t>
-  </si>
-  <si>
-    <t>AMPLIFER configuration</t>
-  </si>
-  <si>
-    <t>XU1,XU20,Xdatamap1</t>
-  </si>
-  <si>
-    <t>LDO configurationA</t>
-  </si>
-  <si>
-    <t>3:0</t>
-  </si>
-  <si>
-    <t>XU1,XU19,Xdatamap2</t>
-  </si>
-  <si>
-    <t>XU1,XU19,Xdatamap1</t>
-  </si>
-  <si>
-    <t>Reference2 output</t>
-  </si>
-  <si>
-    <t>XU1,XSERVICE,Xdatamap2</t>
-  </si>
-  <si>
-    <t>Reference3 output</t>
-  </si>
-  <si>
-    <t>XU1,XSERVICE,Xdatamap1</t>
-  </si>
-  <si>
-    <t>REFERENCE selection for LDO</t>
-  </si>
-  <si>
-    <t>XU1,XSERVICE,Xdatamap4</t>
-  </si>
-  <si>
-    <t>SERVICE configuration</t>
-  </si>
-  <si>
-    <t>5:0</t>
-  </si>
-  <si>
-    <t>XU1,XSERVICE,Xdatamap3</t>
-  </si>
-  <si>
     <t>REGISTER DETAIL ADDRESS REPORT</t>
   </si>
   <si>
@@ -1925,60 +1726,6 @@
     <t>rdl_data</t>
   </si>
   <si>
-    <t>AMP CONTROL High gain adjustmentCode 0x00 1Code 0x01 2Code 0x02 3Code 0x03 4Code 0x04 5Code 0x05 6Code 0x06 7Code 0x07 8</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'AMP_CONTROL_High_gain_adjustment', 'name': 'AMPCONTROLHIGHgain', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>AMP CONTROL Medium gain adjustmentCode 0x00 1Code 0x01 2Code 0x02 3Code 0x03 4Code 0x04 5Code 0x05 6Code 0x06 7Code 0x07 8</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'AMP_CONTROL_Medium_gain_adjustment', 'name': 'AMPCONTROLMEDIUMgain', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>AMP CONTROL Slow gain adjustmentCode 0x00 0.8VCode 0x01 0.96VCode 0x02 1.12VCode 0x03 1.28VCode 0x04 1.44VCode 0x05 1.60VCode 0x06 1.76VCode 0x07 1.92V</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'AMP_CONTROL_Slow_gain_adjustment', 'name': 'AMPCONTROLSLOWgain', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>AMPLIFER configurationBit0 LDO0 0:disable 1:disableBit1 LDO1 0:disable 1:disableBit2 LDO2 0:disable 1:disableBit3 LDO3 0:disable 1:disableBit4 LDO4 0:disable 1:disableBit5 LDO5 0:disable 1:disableBit6 LDO6 0:disable 1:disableBit7 LDO7 0:disable 1:disable</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'LDO0', 'name': 'LDO0', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO1', 'name': 'LDO1', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO2', 'name': 'LDO2', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO3', 'name': 'LDO3', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO4', 'name': 'LDO4', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO5', 'name': 'LDO5', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO6', 'name': 'LDO6', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO7', 'name': 'LDO7', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>LDO configurationABit0 LDO8 0:disable 1:enableBit1 LDO9 0:disable 1:enableBit2 LDO10 0:disable 1:enableBit3 LDO11 0:disable 1:enable</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'LDO8', 'name': 'LDO8', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO9', 'name': 'LDO9', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO10', 'name': 'LDO10', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'LDO11', 'name': 'LDO11', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Reference2 outputCode 0x00 0.68VCode 0x01 0.71VCode 0x02 0.74VCode 0x03 0.78VCode 0x04 0.8VCode 0x05 0.84VCode 0x06 0.87VCode 0x07 0.9V</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'Reference2_output', 'name': 'REF2output', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Reference3 outputCode 0x00 0.6VCode 0x01 0.8VCode 0x02 1.0VCode 0x03 1.8VCode 0x04 2.0VCode 0x05 2.5VCode 0x06 3.3VCode 0x07 4.0V</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'Reference3_output', 'name': 'REF3output', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>REFERENCE selection for LDOCode 0x00 Reference0Code 0x01 Reference1Code 0x02 Reference2Code 0x03 Reference3</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'REFERENCE_selection_for_LDO', 'name': 'REFERENCEselect', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>SERVICE configurationCode 0x00 0.68VCode 0x01 0.71VCode 0x02 0.74VCode 0x03 0.78V</t>
-  </si>
-  <si>
-    <t>{'fields': [{'desc': 'SERVICE_configuration', 'name': 'SERVICEconfiguration', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
     <t>FACTORY ADDRESS REPORT</t>
   </si>
   <si>
@@ -2000,7 +1747,7 @@
     <t>PADs</t>
   </si>
   <si>
-    <t>{"TAEXT": "2", "tdext": "3"}</t>
+    <t>{"TAEXT": "2"}</t>
   </si>
   <si>
     <t>DFT HIJACK ADDRESS REPORT</t>
@@ -2471,52 +2218,52 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2526,52 +2273,47 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>71</v>
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2586,7 +2328,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2606,7 +2348,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2621,7 +2363,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2636,7 +2378,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2656,12 +2398,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2676,212 +2418,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2896,12 +2638,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2916,7 +2658,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2936,127 +2678,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3071,7 +2813,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3336,17 +3078,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +3103,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3381,17 +3123,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3406,52 +3148,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3466,81 +3208,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3548,185 +3290,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B33" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B34" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3734,453 +3476,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B67" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="B68" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B69" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="B70" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B80" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B81" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B84" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="B87" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="B88" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="B89" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B90" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="B95" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B100" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -4188,628 +3930,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B102" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="B103" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="B106" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="B107" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="B108" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="B109" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="B110" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="B112" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="B113" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="B117" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="B118" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="B119" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B120" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="B121" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="B122" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="B123" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="B124" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="B125" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="B126" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="B127" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B128" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="B129" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="B130" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="B131" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B132" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="B133" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="B135" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="B136" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B137" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="B138" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="B139" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B140" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="B141" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B142" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B143" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="B144" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B145" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="B146" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="B147" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B148" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B149" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B150" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B151" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B152" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B153" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B154" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="B155" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B156" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B157" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="B158" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="B159" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="B160" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B161" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="B162" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="B163" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="B164" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="B165" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="B166" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="B167" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="B168" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="B169" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="B170" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="B171" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="B172" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="B173" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="B174" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="B175" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="B176" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="B177" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="B178" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="B179" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="B180" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4824,47 +4566,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4872,15 +4614,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4888,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -4898,280 +4640,31 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D5" t="s">
-        <v>445</v>
-      </c>
-      <c r="E5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" t="s">
-        <v>445</v>
-      </c>
-      <c r="E6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" t="s">
-        <v>447</v>
-      </c>
-      <c r="C7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E7" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" t="s">
-        <v>448</v>
-      </c>
-      <c r="C8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" t="s">
-        <v>445</v>
-      </c>
-      <c r="E8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" t="s">
-        <v>449</v>
-      </c>
-      <c r="C9" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" t="s">
-        <v>445</v>
-      </c>
-      <c r="E9" t="s">
-        <v>433</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" t="s">
-        <v>449</v>
-      </c>
-      <c r="C10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" t="s">
-        <v>445</v>
-      </c>
-      <c r="E10" t="s">
-        <v>433</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" t="s">
-        <v>450</v>
-      </c>
-      <c r="C11" t="s">
-        <v>347</v>
-      </c>
-      <c r="D11" t="s">
-        <v>445</v>
-      </c>
-      <c r="E11" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" t="s">
-        <v>451</v>
-      </c>
-      <c r="C12" t="s">
-        <v>349</v>
-      </c>
-      <c r="D12" t="s">
-        <v>445</v>
-      </c>
-      <c r="E12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" t="s">
-        <v>452</v>
-      </c>
-      <c r="C13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D13" t="s">
-        <v>445</v>
-      </c>
-      <c r="E13" t="s">
-        <v>311</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" t="s">
-        <v>454</v>
-      </c>
-      <c r="C14" t="s">
-        <v>455</v>
-      </c>
-      <c r="D14" t="s">
-        <v>445</v>
-      </c>
-      <c r="E14" t="s">
-        <v>227</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C15" t="s">
-        <v>457</v>
-      </c>
-      <c r="D15" t="s">
-        <v>458</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" t="s">
-        <v>456</v>
-      </c>
-      <c r="C16" t="s">
-        <v>459</v>
-      </c>
-      <c r="D16" t="s">
-        <v>458</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>239</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -5181,31 +4674,249 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>426</v>
+      </c>
+      <c r="B8" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>428</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B9" t="s">
         <v>429</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>436</v>
+      </c>
+      <c r="B14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>438</v>
+      </c>
+      <c r="B16" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>439</v>
+      </c>
+      <c r="B17" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>440</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>431</v>
+      <c r="B18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>441</v>
+      </c>
+      <c r="B19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>442</v>
+      </c>
+      <c r="B20" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>443</v>
+      </c>
+      <c r="B21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>444</v>
+      </c>
+      <c r="B22" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>445</v>
+      </c>
+      <c r="B23" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>446</v>
+      </c>
+      <c r="B24" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>448</v>
+      </c>
+      <c r="B26" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>449</v>
+      </c>
+      <c r="B27" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>450</v>
+      </c>
+      <c r="B28" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B29" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>452</v>
+      </c>
+      <c r="B30" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>453</v>
+      </c>
+      <c r="B31" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>454</v>
+      </c>
+      <c r="B32" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -5215,249 +4926,1169 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="H4" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>468</v>
+      </c>
+      <c r="C5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H5" t="s">
+        <v>471</v>
+      </c>
+      <c r="I5" t="s">
+        <v>472</v>
+      </c>
+      <c r="J5" t="s">
+        <v>473</v>
+      </c>
+      <c r="K5" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>466</v>
+        <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>475</v>
+      </c>
+      <c r="C6" t="s">
+        <v>476</v>
+      </c>
+      <c r="D6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" t="s">
+        <v>470</v>
+      </c>
+      <c r="F6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" t="s">
+        <v>470</v>
+      </c>
+      <c r="H6" t="s">
+        <v>471</v>
+      </c>
+      <c r="I6" t="s">
+        <v>477</v>
+      </c>
+      <c r="J6" t="s">
+        <v>473</v>
+      </c>
+      <c r="K6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" t="s">
+        <v>473</v>
+      </c>
+      <c r="E7" t="s">
+        <v>473</v>
+      </c>
+      <c r="F7" t="s">
+        <v>473</v>
+      </c>
+      <c r="G7" t="s">
+        <v>473</v>
+      </c>
+      <c r="H7" t="s">
+        <v>473</v>
+      </c>
+      <c r="I7" t="s">
+        <v>473</v>
+      </c>
+      <c r="J7" t="s">
+        <v>473</v>
+      </c>
+      <c r="K7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>409</v>
+      </c>
+      <c r="B8" t="s">
+        <v>470</v>
+      </c>
+      <c r="C8" t="s">
+        <v>481</v>
+      </c>
+      <c r="D8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" t="s">
+        <v>470</v>
+      </c>
+      <c r="F8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G8" t="s">
+        <v>470</v>
+      </c>
+      <c r="H8" t="s">
+        <v>471</v>
+      </c>
+      <c r="J8" t="s">
+        <v>473</v>
+      </c>
+      <c r="K8" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" t="s">
+        <v>479</v>
+      </c>
+      <c r="C9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E9" t="s">
+        <v>473</v>
+      </c>
+      <c r="F9" t="s">
+        <v>473</v>
+      </c>
+      <c r="G9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H9" t="s">
+        <v>473</v>
+      </c>
+      <c r="I9" t="s">
+        <v>473</v>
+      </c>
+      <c r="J9" t="s">
+        <v>473</v>
+      </c>
+      <c r="K9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" t="s">
+        <v>479</v>
+      </c>
+      <c r="C10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F10" t="s">
+        <v>473</v>
+      </c>
+      <c r="G10" t="s">
+        <v>473</v>
+      </c>
+      <c r="H10" t="s">
+        <v>473</v>
+      </c>
+      <c r="I10" t="s">
+        <v>473</v>
+      </c>
+      <c r="J10" t="s">
+        <v>473</v>
+      </c>
+      <c r="K10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" t="s">
+        <v>479</v>
+      </c>
+      <c r="C11" t="s">
+        <v>480</v>
+      </c>
+      <c r="D11" t="s">
+        <v>473</v>
+      </c>
+      <c r="E11" t="s">
+        <v>473</v>
+      </c>
+      <c r="F11" t="s">
+        <v>473</v>
+      </c>
+      <c r="G11" t="s">
+        <v>473</v>
+      </c>
+      <c r="H11" t="s">
+        <v>473</v>
+      </c>
+      <c r="I11" t="s">
+        <v>473</v>
+      </c>
+      <c r="J11" t="s">
+        <v>473</v>
+      </c>
+      <c r="K11" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" t="s">
+        <v>479</v>
+      </c>
+      <c r="C12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D12" t="s">
+        <v>473</v>
+      </c>
+      <c r="E12" t="s">
+        <v>473</v>
+      </c>
+      <c r="F12" t="s">
+        <v>473</v>
+      </c>
+      <c r="G12" t="s">
+        <v>473</v>
+      </c>
+      <c r="H12" t="s">
+        <v>473</v>
+      </c>
+      <c r="I12" t="s">
+        <v>473</v>
+      </c>
+      <c r="J12" t="s">
+        <v>473</v>
+      </c>
+      <c r="K12" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>482</v>
+      </c>
+      <c r="B13" t="s">
+        <v>479</v>
+      </c>
+      <c r="C13" t="s">
+        <v>480</v>
+      </c>
+      <c r="D13" t="s">
+        <v>473</v>
+      </c>
+      <c r="E13" t="s">
+        <v>473</v>
+      </c>
+      <c r="F13" t="s">
+        <v>473</v>
+      </c>
+      <c r="G13" t="s">
+        <v>473</v>
+      </c>
+      <c r="H13" t="s">
+        <v>473</v>
+      </c>
+      <c r="I13" t="s">
+        <v>473</v>
+      </c>
+      <c r="J13" t="s">
+        <v>473</v>
+      </c>
+      <c r="K13" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" t="s">
+        <v>479</v>
+      </c>
+      <c r="C14" t="s">
+        <v>480</v>
+      </c>
+      <c r="D14" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" t="s">
+        <v>473</v>
+      </c>
+      <c r="F14" t="s">
+        <v>473</v>
+      </c>
+      <c r="G14" t="s">
+        <v>473</v>
+      </c>
+      <c r="H14" t="s">
+        <v>473</v>
+      </c>
+      <c r="I14" t="s">
+        <v>473</v>
+      </c>
+      <c r="J14" t="s">
+        <v>473</v>
+      </c>
+      <c r="K14" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>483</v>
+      </c>
+      <c r="B15" t="s">
+        <v>479</v>
+      </c>
+      <c r="C15" t="s">
+        <v>480</v>
+      </c>
+      <c r="D15" t="s">
+        <v>473</v>
+      </c>
+      <c r="E15" t="s">
+        <v>473</v>
+      </c>
+      <c r="F15" t="s">
+        <v>473</v>
+      </c>
+      <c r="G15" t="s">
+        <v>473</v>
+      </c>
+      <c r="H15" t="s">
+        <v>473</v>
+      </c>
+      <c r="I15" t="s">
+        <v>473</v>
+      </c>
+      <c r="J15" t="s">
+        <v>473</v>
+      </c>
+      <c r="K15" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>484</v>
+      </c>
+      <c r="B16" t="s">
+        <v>485</v>
+      </c>
+      <c r="C16" t="s">
+        <v>486</v>
+      </c>
+      <c r="D16" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" t="s">
+        <v>470</v>
+      </c>
+      <c r="F16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" t="s">
         <v>468</v>
       </c>
-      <c r="B7" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="H16" t="s">
+        <v>471</v>
+      </c>
+      <c r="I16" t="s">
+        <v>487</v>
+      </c>
+      <c r="J16" t="s">
+        <v>473</v>
+      </c>
+      <c r="K16" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>433</v>
+      </c>
+      <c r="B17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C17" t="s">
+        <v>488</v>
+      </c>
+      <c r="D17" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" t="s">
         <v>470</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F17" t="s">
+        <v>243</v>
+      </c>
+      <c r="G17" t="s">
+        <v>468</v>
+      </c>
+      <c r="H17" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>472</v>
-      </c>
-      <c r="B9" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="I17" t="s">
+        <v>489</v>
+      </c>
+      <c r="J17" t="s">
+        <v>473</v>
+      </c>
+      <c r="K17" t="s">
         <v>474</v>
       </c>
-      <c r="B10" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>476</v>
-      </c>
-      <c r="B11" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>478</v>
-      </c>
-      <c r="B12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>490</v>
+      </c>
+      <c r="B18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C18" t="s">
+        <v>491</v>
+      </c>
+      <c r="D18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" t="s">
+        <v>470</v>
+      </c>
+      <c r="F18" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" t="s">
+        <v>468</v>
+      </c>
+      <c r="H18" t="s">
+        <v>471</v>
+      </c>
+      <c r="I18" t="s">
+        <v>492</v>
+      </c>
+      <c r="J18" t="s">
+        <v>473</v>
+      </c>
+      <c r="K18" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>493</v>
+      </c>
+      <c r="B19" t="s">
+        <v>494</v>
+      </c>
+      <c r="C19" t="s">
+        <v>494</v>
+      </c>
+      <c r="D19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" t="s">
+        <v>470</v>
+      </c>
+      <c r="F19" t="s">
+        <v>243</v>
+      </c>
+      <c r="G19" t="s">
+        <v>468</v>
+      </c>
+      <c r="H19" t="s">
+        <v>471</v>
+      </c>
+      <c r="I19" t="s">
+        <v>495</v>
+      </c>
+      <c r="J19" t="s">
+        <v>473</v>
+      </c>
+      <c r="K19" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>496</v>
+      </c>
+      <c r="B20" t="s">
         <v>479</v>
       </c>
-      <c r="B13" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="C20" t="s">
         <v>480</v>
       </c>
-      <c r="B14" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>481</v>
-      </c>
-      <c r="B15" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>482</v>
-      </c>
-      <c r="B16" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>483</v>
-      </c>
-      <c r="B17" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>484</v>
-      </c>
-      <c r="B18" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>485</v>
-      </c>
-      <c r="B19" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>486</v>
-      </c>
-      <c r="B20" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="D20" t="s">
+        <v>473</v>
+      </c>
+      <c r="E20" t="s">
+        <v>473</v>
+      </c>
+      <c r="F20" t="s">
+        <v>473</v>
+      </c>
+      <c r="G20" t="s">
+        <v>473</v>
+      </c>
+      <c r="H20" t="s">
+        <v>473</v>
+      </c>
+      <c r="I20" t="s">
+        <v>473</v>
+      </c>
+      <c r="J20" t="s">
+        <v>473</v>
+      </c>
+      <c r="K20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>479</v>
+      </c>
+      <c r="C21" t="s">
+        <v>480</v>
+      </c>
+      <c r="D21" t="s">
+        <v>473</v>
+      </c>
+      <c r="E21" t="s">
+        <v>473</v>
+      </c>
+      <c r="F21" t="s">
+        <v>473</v>
+      </c>
+      <c r="G21" t="s">
+        <v>473</v>
+      </c>
+      <c r="H21" t="s">
+        <v>473</v>
+      </c>
+      <c r="I21" t="s">
+        <v>473</v>
+      </c>
+      <c r="J21" t="s">
+        <v>473</v>
+      </c>
+      <c r="K21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="B22" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>479</v>
+      </c>
+      <c r="C22" t="s">
+        <v>480</v>
+      </c>
+      <c r="D22" t="s">
+        <v>473</v>
+      </c>
+      <c r="E22" t="s">
+        <v>473</v>
+      </c>
+      <c r="F22" t="s">
+        <v>473</v>
+      </c>
+      <c r="G22" t="s">
+        <v>473</v>
+      </c>
+      <c r="H22" t="s">
+        <v>473</v>
+      </c>
+      <c r="I22" t="s">
+        <v>473</v>
+      </c>
+      <c r="J22" t="s">
+        <v>473</v>
+      </c>
+      <c r="K22" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>489</v>
+        <v>431</v>
       </c>
       <c r="B23" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>499</v>
+      </c>
+      <c r="C23" t="s">
+        <v>499</v>
+      </c>
+      <c r="D23" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" t="s">
+        <v>470</v>
+      </c>
+      <c r="F23" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" t="s">
+        <v>468</v>
+      </c>
+      <c r="H23" t="s">
+        <v>471</v>
+      </c>
+      <c r="I23" t="s">
+        <v>500</v>
+      </c>
+      <c r="J23" t="s">
+        <v>473</v>
+      </c>
+      <c r="K23" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B24" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>502</v>
+      </c>
+      <c r="C24" t="s">
+        <v>503</v>
+      </c>
+      <c r="D24" t="s">
+        <v>245</v>
+      </c>
+      <c r="E24" t="s">
+        <v>470</v>
+      </c>
+      <c r="F24" t="s">
+        <v>243</v>
+      </c>
+      <c r="G24" t="s">
+        <v>468</v>
+      </c>
+      <c r="H24" t="s">
+        <v>471</v>
+      </c>
+      <c r="I24" t="s">
+        <v>504</v>
+      </c>
+      <c r="J24" t="s">
+        <v>473</v>
+      </c>
+      <c r="K24" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="B25" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>506</v>
+      </c>
+      <c r="C25" t="s">
+        <v>506</v>
+      </c>
+      <c r="D25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" t="s">
+        <v>470</v>
+      </c>
+      <c r="F25" t="s">
+        <v>243</v>
+      </c>
+      <c r="G25" t="s">
+        <v>468</v>
+      </c>
+      <c r="H25" t="s">
+        <v>471</v>
+      </c>
+      <c r="I25" t="s">
+        <v>507</v>
+      </c>
+      <c r="J25" t="s">
+        <v>473</v>
+      </c>
+      <c r="K25" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="B26" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>509</v>
+      </c>
+      <c r="C26" t="s">
+        <v>509</v>
+      </c>
+      <c r="D26" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" t="s">
+        <v>470</v>
+      </c>
+      <c r="F26" t="s">
+        <v>243</v>
+      </c>
+      <c r="G26" t="s">
+        <v>468</v>
+      </c>
+      <c r="H26" t="s">
+        <v>471</v>
+      </c>
+      <c r="I26" t="s">
+        <v>510</v>
+      </c>
+      <c r="J26" t="s">
+        <v>473</v>
+      </c>
+      <c r="K26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B27" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>512</v>
+      </c>
+      <c r="C27" t="s">
+        <v>512</v>
+      </c>
+      <c r="D27" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" t="s">
+        <v>470</v>
+      </c>
+      <c r="F27" t="s">
+        <v>243</v>
+      </c>
+      <c r="G27" t="s">
+        <v>468</v>
+      </c>
+      <c r="H27" t="s">
+        <v>471</v>
+      </c>
+      <c r="I27" t="s">
+        <v>513</v>
+      </c>
+      <c r="J27" t="s">
+        <v>473</v>
+      </c>
+      <c r="K27" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="B28" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>479</v>
+      </c>
+      <c r="C28" t="s">
+        <v>480</v>
+      </c>
+      <c r="D28" t="s">
+        <v>473</v>
+      </c>
+      <c r="E28" t="s">
+        <v>473</v>
+      </c>
+      <c r="F28" t="s">
+        <v>473</v>
+      </c>
+      <c r="G28" t="s">
+        <v>473</v>
+      </c>
+      <c r="H28" t="s">
+        <v>473</v>
+      </c>
+      <c r="I28" t="s">
+        <v>473</v>
+      </c>
+      <c r="J28" t="s">
+        <v>473</v>
+      </c>
+      <c r="K28" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="B29" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>515</v>
+      </c>
+      <c r="C29" t="s">
+        <v>515</v>
+      </c>
+      <c r="D29" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" t="s">
+        <v>470</v>
+      </c>
+      <c r="F29" t="s">
+        <v>243</v>
+      </c>
+      <c r="G29" t="s">
+        <v>468</v>
+      </c>
+      <c r="H29" t="s">
+        <v>471</v>
+      </c>
+      <c r="I29" t="s">
+        <v>516</v>
+      </c>
+      <c r="J29" t="s">
+        <v>473</v>
+      </c>
+      <c r="K29" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B30" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>518</v>
+      </c>
+      <c r="C30" t="s">
+        <v>518</v>
+      </c>
+      <c r="D30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E30" t="s">
+        <v>470</v>
+      </c>
+      <c r="F30" t="s">
+        <v>243</v>
+      </c>
+      <c r="G30" t="s">
+        <v>468</v>
+      </c>
+      <c r="H30" t="s">
+        <v>471</v>
+      </c>
+      <c r="I30" t="s">
+        <v>519</v>
+      </c>
+      <c r="J30" t="s">
+        <v>473</v>
+      </c>
+      <c r="K30" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="B31" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>521</v>
+      </c>
+      <c r="C31" t="s">
+        <v>521</v>
+      </c>
+      <c r="D31" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" t="s">
+        <v>470</v>
+      </c>
+      <c r="F31" t="s">
+        <v>243</v>
+      </c>
+      <c r="G31" t="s">
+        <v>468</v>
+      </c>
+      <c r="H31" t="s">
+        <v>471</v>
+      </c>
+      <c r="I31" t="s">
+        <v>522</v>
+      </c>
+      <c r="J31" t="s">
+        <v>473</v>
+      </c>
+      <c r="K31" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="B32" t="s">
-        <v>434</v>
+        <v>524</v>
+      </c>
+      <c r="C32" t="s">
+        <v>524</v>
+      </c>
+      <c r="D32" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" t="s">
+        <v>470</v>
+      </c>
+      <c r="F32" t="s">
+        <v>243</v>
+      </c>
+      <c r="G32" t="s">
+        <v>468</v>
+      </c>
+      <c r="H32" t="s">
+        <v>471</v>
+      </c>
+      <c r="I32" t="s">
+        <v>525</v>
+      </c>
+      <c r="J32" t="s">
+        <v>473</v>
+      </c>
+      <c r="K32" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>526</v>
+      </c>
+      <c r="B33" t="s">
+        <v>527</v>
+      </c>
+      <c r="C33" t="s">
+        <v>527</v>
+      </c>
+      <c r="D33" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" t="s">
+        <v>470</v>
+      </c>
+      <c r="F33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G33" t="s">
+        <v>468</v>
+      </c>
+      <c r="H33" t="s">
+        <v>471</v>
+      </c>
+      <c r="I33" t="s">
+        <v>528</v>
+      </c>
+      <c r="J33" t="s">
+        <v>473</v>
+      </c>
+      <c r="K33" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>529</v>
+      </c>
+      <c r="B34" t="s">
+        <v>530</v>
+      </c>
+      <c r="C34" t="s">
+        <v>530</v>
+      </c>
+      <c r="D34" t="s">
+        <v>245</v>
+      </c>
+      <c r="E34" t="s">
+        <v>470</v>
+      </c>
+      <c r="F34" t="s">
+        <v>243</v>
+      </c>
+      <c r="G34" t="s">
+        <v>468</v>
+      </c>
+      <c r="H34" t="s">
+        <v>471</v>
+      </c>
+      <c r="I34" t="s">
+        <v>531</v>
+      </c>
+      <c r="J34" t="s">
+        <v>473</v>
+      </c>
+      <c r="K34" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>532</v>
+      </c>
+      <c r="B35" t="s">
+        <v>533</v>
+      </c>
+      <c r="C35" t="s">
+        <v>533</v>
+      </c>
+      <c r="D35" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" t="s">
+        <v>470</v>
+      </c>
+      <c r="F35" t="s">
+        <v>243</v>
+      </c>
+      <c r="G35" t="s">
+        <v>468</v>
+      </c>
+      <c r="H35" t="s">
+        <v>471</v>
+      </c>
+      <c r="I35" t="s">
+        <v>534</v>
+      </c>
+      <c r="J35" t="s">
+        <v>473</v>
+      </c>
+      <c r="K35" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" t="s">
+        <v>479</v>
+      </c>
+      <c r="C36" t="s">
+        <v>480</v>
+      </c>
+      <c r="D36" t="s">
+        <v>473</v>
+      </c>
+      <c r="E36" t="s">
+        <v>473</v>
+      </c>
+      <c r="F36" t="s">
+        <v>473</v>
+      </c>
+      <c r="G36" t="s">
+        <v>473</v>
+      </c>
+      <c r="H36" t="s">
+        <v>473</v>
+      </c>
+      <c r="I36" t="s">
+        <v>473</v>
+      </c>
+      <c r="J36" t="s">
+        <v>473</v>
+      </c>
+      <c r="K36" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -5467,1169 +6098,135 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>502</v>
+        <v>459</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>503</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>434</v>
+        <v>541</v>
       </c>
       <c r="B5" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="C5" t="s">
-        <v>513</v>
+        <v>302</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
       <c r="E5" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="F5" t="s">
-        <v>227</v>
+        <v>544</v>
       </c>
       <c r="G5" t="s">
-        <v>514</v>
-      </c>
-      <c r="H5" t="s">
-        <v>515</v>
-      </c>
-      <c r="I5" t="s">
-        <v>516</v>
-      </c>
-      <c r="J5" t="s">
-        <v>517</v>
-      </c>
-      <c r="K5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>545</v>
       </c>
       <c r="B6" t="s">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="C6" t="s">
-        <v>520</v>
+        <v>302</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="E6" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="F6" t="s">
-        <v>227</v>
+        <v>544</v>
       </c>
       <c r="G6" t="s">
-        <v>514</v>
-      </c>
-      <c r="H6" t="s">
-        <v>515</v>
-      </c>
-      <c r="I6" t="s">
-        <v>521</v>
-      </c>
-      <c r="J6" t="s">
-        <v>517</v>
-      </c>
-      <c r="K6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>311</v>
+        <v>547</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="C7" t="s">
-        <v>524</v>
+        <v>302</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="E7" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>544</v>
       </c>
       <c r="G7" t="s">
-        <v>514</v>
-      </c>
-      <c r="H7" t="s">
-        <v>515</v>
-      </c>
-      <c r="I7" t="s">
-        <v>525</v>
-      </c>
-      <c r="J7" t="s">
-        <v>517</v>
-      </c>
-      <c r="K7" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>433</v>
+        <v>549</v>
       </c>
       <c r="B8" t="s">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="C8" t="s">
-        <v>526</v>
+        <v>302</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>328</v>
       </c>
       <c r="E8" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
+        <v>544</v>
       </c>
       <c r="G8" t="s">
-        <v>514</v>
-      </c>
-      <c r="H8" t="s">
-        <v>515</v>
-      </c>
-      <c r="J8" t="s">
-        <v>517</v>
-      </c>
-      <c r="K8" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>313</v>
-      </c>
-      <c r="B9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C9" t="s">
-        <v>528</v>
-      </c>
-      <c r="D9" t="s">
-        <v>517</v>
-      </c>
-      <c r="E9" t="s">
-        <v>517</v>
-      </c>
-      <c r="F9" t="s">
-        <v>517</v>
-      </c>
-      <c r="G9" t="s">
-        <v>517</v>
-      </c>
-      <c r="H9" t="s">
-        <v>517</v>
-      </c>
-      <c r="I9" t="s">
-        <v>517</v>
-      </c>
-      <c r="J9" t="s">
-        <v>517</v>
-      </c>
-      <c r="K9" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" t="s">
-        <v>527</v>
-      </c>
-      <c r="C10" t="s">
-        <v>528</v>
-      </c>
-      <c r="D10" t="s">
-        <v>517</v>
-      </c>
-      <c r="E10" t="s">
-        <v>517</v>
-      </c>
-      <c r="F10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G10" t="s">
-        <v>517</v>
-      </c>
-      <c r="H10" t="s">
-        <v>517</v>
-      </c>
-      <c r="I10" t="s">
-        <v>517</v>
-      </c>
-      <c r="J10" t="s">
-        <v>517</v>
-      </c>
-      <c r="K10" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>432</v>
-      </c>
-      <c r="B11" t="s">
-        <v>527</v>
-      </c>
-      <c r="C11" t="s">
-        <v>528</v>
-      </c>
-      <c r="D11" t="s">
-        <v>517</v>
-      </c>
-      <c r="E11" t="s">
-        <v>517</v>
-      </c>
-      <c r="F11" t="s">
-        <v>517</v>
-      </c>
-      <c r="G11" t="s">
-        <v>517</v>
-      </c>
-      <c r="H11" t="s">
-        <v>517</v>
-      </c>
-      <c r="I11" t="s">
-        <v>517</v>
-      </c>
-      <c r="J11" t="s">
-        <v>517</v>
-      </c>
-      <c r="K11" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>250</v>
-      </c>
-      <c r="B12" t="s">
-        <v>527</v>
-      </c>
-      <c r="C12" t="s">
-        <v>528</v>
-      </c>
-      <c r="D12" t="s">
-        <v>517</v>
-      </c>
-      <c r="E12" t="s">
-        <v>517</v>
-      </c>
-      <c r="F12" t="s">
-        <v>517</v>
-      </c>
-      <c r="G12" t="s">
-        <v>517</v>
-      </c>
-      <c r="H12" t="s">
-        <v>517</v>
-      </c>
-      <c r="I12" t="s">
-        <v>517</v>
-      </c>
-      <c r="J12" t="s">
-        <v>517</v>
-      </c>
-      <c r="K12" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>529</v>
-      </c>
-      <c r="B13" t="s">
-        <v>527</v>
-      </c>
-      <c r="C13" t="s">
-        <v>528</v>
-      </c>
-      <c r="D13" t="s">
-        <v>517</v>
-      </c>
-      <c r="E13" t="s">
-        <v>517</v>
-      </c>
-      <c r="F13" t="s">
-        <v>517</v>
-      </c>
-      <c r="G13" t="s">
-        <v>517</v>
-      </c>
-      <c r="H13" t="s">
-        <v>517</v>
-      </c>
-      <c r="I13" t="s">
-        <v>517</v>
-      </c>
-      <c r="J13" t="s">
-        <v>517</v>
-      </c>
-      <c r="K13" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>321</v>
-      </c>
-      <c r="B14" t="s">
-        <v>527</v>
-      </c>
-      <c r="C14" t="s">
-        <v>528</v>
-      </c>
-      <c r="D14" t="s">
-        <v>517</v>
-      </c>
-      <c r="E14" t="s">
-        <v>517</v>
-      </c>
-      <c r="F14" t="s">
-        <v>517</v>
-      </c>
-      <c r="G14" t="s">
-        <v>517</v>
-      </c>
-      <c r="H14" t="s">
-        <v>517</v>
-      </c>
-      <c r="I14" t="s">
-        <v>517</v>
-      </c>
-      <c r="J14" t="s">
-        <v>517</v>
-      </c>
-      <c r="K14" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>530</v>
-      </c>
-      <c r="B15" t="s">
-        <v>527</v>
-      </c>
-      <c r="C15" t="s">
-        <v>528</v>
-      </c>
-      <c r="D15" t="s">
-        <v>517</v>
-      </c>
-      <c r="E15" t="s">
-        <v>517</v>
-      </c>
-      <c r="F15" t="s">
-        <v>517</v>
-      </c>
-      <c r="G15" t="s">
-        <v>517</v>
-      </c>
-      <c r="H15" t="s">
-        <v>517</v>
-      </c>
-      <c r="I15" t="s">
-        <v>517</v>
-      </c>
-      <c r="J15" t="s">
-        <v>517</v>
-      </c>
-      <c r="K15" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>531</v>
-      </c>
-      <c r="B16" t="s">
-        <v>532</v>
-      </c>
-      <c r="C16" t="s">
-        <v>533</v>
-      </c>
-      <c r="D16" t="s">
-        <v>269</v>
-      </c>
-      <c r="E16" t="s">
-        <v>514</v>
-      </c>
-      <c r="F16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G16" t="s">
-        <v>512</v>
-      </c>
-      <c r="H16" t="s">
-        <v>515</v>
-      </c>
-      <c r="I16" t="s">
-        <v>534</v>
-      </c>
-      <c r="J16" t="s">
-        <v>517</v>
-      </c>
-      <c r="K16" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>477</v>
-      </c>
-      <c r="B17" t="s">
-        <v>535</v>
-      </c>
-      <c r="C17" t="s">
-        <v>535</v>
-      </c>
-      <c r="D17" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" t="s">
-        <v>514</v>
-      </c>
-      <c r="F17" t="s">
-        <v>267</v>
-      </c>
-      <c r="G17" t="s">
-        <v>512</v>
-      </c>
-      <c r="H17" t="s">
-        <v>515</v>
-      </c>
-      <c r="I17" t="s">
-        <v>536</v>
-      </c>
-      <c r="J17" t="s">
-        <v>517</v>
-      </c>
-      <c r="K17" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>537</v>
-      </c>
-      <c r="B18" t="s">
-        <v>538</v>
-      </c>
-      <c r="C18" t="s">
-        <v>538</v>
-      </c>
-      <c r="D18" t="s">
-        <v>269</v>
-      </c>
-      <c r="E18" t="s">
-        <v>514</v>
-      </c>
-      <c r="F18" t="s">
-        <v>267</v>
-      </c>
-      <c r="G18" t="s">
-        <v>512</v>
-      </c>
-      <c r="H18" t="s">
-        <v>515</v>
-      </c>
-      <c r="I18" t="s">
-        <v>539</v>
-      </c>
-      <c r="J18" t="s">
-        <v>517</v>
-      </c>
-      <c r="K18" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>540</v>
-      </c>
-      <c r="B19" t="s">
-        <v>541</v>
-      </c>
-      <c r="C19" t="s">
-        <v>541</v>
-      </c>
-      <c r="D19" t="s">
-        <v>269</v>
-      </c>
-      <c r="E19" t="s">
-        <v>514</v>
-      </c>
-      <c r="F19" t="s">
-        <v>267</v>
-      </c>
-      <c r="G19" t="s">
-        <v>512</v>
-      </c>
-      <c r="H19" t="s">
-        <v>515</v>
-      </c>
-      <c r="I19" t="s">
-        <v>542</v>
-      </c>
-      <c r="J19" t="s">
-        <v>517</v>
-      </c>
-      <c r="K19" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>543</v>
-      </c>
-      <c r="B20" t="s">
-        <v>527</v>
-      </c>
-      <c r="C20" t="s">
-        <v>528</v>
-      </c>
-      <c r="D20" t="s">
-        <v>517</v>
-      </c>
-      <c r="E20" t="s">
-        <v>517</v>
-      </c>
-      <c r="F20" t="s">
-        <v>517</v>
-      </c>
-      <c r="G20" t="s">
-        <v>517</v>
-      </c>
-      <c r="H20" t="s">
-        <v>517</v>
-      </c>
-      <c r="I20" t="s">
-        <v>517</v>
-      </c>
-      <c r="J20" t="s">
-        <v>517</v>
-      </c>
-      <c r="K20" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>544</v>
-      </c>
-      <c r="B21" t="s">
-        <v>527</v>
-      </c>
-      <c r="C21" t="s">
-        <v>528</v>
-      </c>
-      <c r="D21" t="s">
-        <v>517</v>
-      </c>
-      <c r="E21" t="s">
-        <v>517</v>
-      </c>
-      <c r="F21" t="s">
-        <v>517</v>
-      </c>
-      <c r="G21" t="s">
-        <v>517</v>
-      </c>
-      <c r="H21" t="s">
-        <v>517</v>
-      </c>
-      <c r="I21" t="s">
-        <v>517</v>
-      </c>
-      <c r="J21" t="s">
-        <v>517</v>
-      </c>
-      <c r="K21" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>545</v>
-      </c>
-      <c r="B22" t="s">
-        <v>527</v>
-      </c>
-      <c r="C22" t="s">
-        <v>528</v>
-      </c>
-      <c r="D22" t="s">
-        <v>517</v>
-      </c>
-      <c r="E22" t="s">
-        <v>517</v>
-      </c>
-      <c r="F22" t="s">
-        <v>517</v>
-      </c>
-      <c r="G22" t="s">
-        <v>517</v>
-      </c>
-      <c r="H22" t="s">
-        <v>517</v>
-      </c>
-      <c r="I22" t="s">
-        <v>517</v>
-      </c>
-      <c r="J22" t="s">
-        <v>517</v>
-      </c>
-      <c r="K22" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>475</v>
-      </c>
-      <c r="B23" t="s">
-        <v>546</v>
-      </c>
-      <c r="C23" t="s">
-        <v>546</v>
-      </c>
-      <c r="D23" t="s">
-        <v>269</v>
-      </c>
-      <c r="E23" t="s">
-        <v>514</v>
-      </c>
-      <c r="F23" t="s">
-        <v>267</v>
-      </c>
-      <c r="G23" t="s">
-        <v>512</v>
-      </c>
-      <c r="H23" t="s">
-        <v>515</v>
-      </c>
-      <c r="I23" t="s">
-        <v>547</v>
-      </c>
-      <c r="J23" t="s">
-        <v>517</v>
-      </c>
-      <c r="K23" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>548</v>
-      </c>
-      <c r="B24" t="s">
-        <v>549</v>
-      </c>
-      <c r="C24" t="s">
-        <v>550</v>
-      </c>
-      <c r="D24" t="s">
-        <v>269</v>
-      </c>
-      <c r="E24" t="s">
-        <v>514</v>
-      </c>
-      <c r="F24" t="s">
-        <v>267</v>
-      </c>
-      <c r="G24" t="s">
-        <v>512</v>
-      </c>
-      <c r="H24" t="s">
-        <v>515</v>
-      </c>
-      <c r="I24" t="s">
-        <v>551</v>
-      </c>
-      <c r="J24" t="s">
-        <v>517</v>
-      </c>
-      <c r="K24" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>552</v>
-      </c>
-      <c r="B25" t="s">
-        <v>553</v>
-      </c>
-      <c r="C25" t="s">
-        <v>553</v>
-      </c>
-      <c r="D25" t="s">
-        <v>269</v>
-      </c>
-      <c r="E25" t="s">
-        <v>514</v>
-      </c>
-      <c r="F25" t="s">
-        <v>267</v>
-      </c>
-      <c r="G25" t="s">
-        <v>512</v>
-      </c>
-      <c r="H25" t="s">
-        <v>515</v>
-      </c>
-      <c r="I25" t="s">
-        <v>554</v>
-      </c>
-      <c r="J25" t="s">
-        <v>517</v>
-      </c>
-      <c r="K25" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>555</v>
-      </c>
-      <c r="B26" t="s">
-        <v>556</v>
-      </c>
-      <c r="C26" t="s">
-        <v>556</v>
-      </c>
-      <c r="D26" t="s">
-        <v>269</v>
-      </c>
-      <c r="E26" t="s">
-        <v>514</v>
-      </c>
-      <c r="F26" t="s">
-        <v>267</v>
-      </c>
-      <c r="G26" t="s">
-        <v>512</v>
-      </c>
-      <c r="H26" t="s">
-        <v>515</v>
-      </c>
-      <c r="I26" t="s">
-        <v>557</v>
-      </c>
-      <c r="J26" t="s">
-        <v>517</v>
-      </c>
-      <c r="K26" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>558</v>
-      </c>
-      <c r="B27" t="s">
-        <v>559</v>
-      </c>
-      <c r="C27" t="s">
-        <v>559</v>
-      </c>
-      <c r="D27" t="s">
-        <v>269</v>
-      </c>
-      <c r="E27" t="s">
-        <v>514</v>
-      </c>
-      <c r="F27" t="s">
-        <v>267</v>
-      </c>
-      <c r="G27" t="s">
-        <v>512</v>
-      </c>
-      <c r="H27" t="s">
-        <v>515</v>
-      </c>
-      <c r="I27" t="s">
-        <v>560</v>
-      </c>
-      <c r="J27" t="s">
-        <v>517</v>
-      </c>
-      <c r="K27" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" t="s">
-        <v>561</v>
-      </c>
-      <c r="B28" t="s">
-        <v>527</v>
-      </c>
-      <c r="C28" t="s">
-        <v>528</v>
-      </c>
-      <c r="D28" t="s">
-        <v>517</v>
-      </c>
-      <c r="E28" t="s">
-        <v>517</v>
-      </c>
-      <c r="F28" t="s">
-        <v>517</v>
-      </c>
-      <c r="G28" t="s">
-        <v>517</v>
-      </c>
-      <c r="H28" t="s">
-        <v>517</v>
-      </c>
-      <c r="I28" t="s">
-        <v>517</v>
-      </c>
-      <c r="J28" t="s">
-        <v>517</v>
-      </c>
-      <c r="K28" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>473</v>
-      </c>
-      <c r="B29" t="s">
-        <v>562</v>
-      </c>
-      <c r="C29" t="s">
-        <v>562</v>
-      </c>
-      <c r="D29" t="s">
-        <v>269</v>
-      </c>
-      <c r="E29" t="s">
-        <v>514</v>
-      </c>
-      <c r="F29" t="s">
-        <v>267</v>
-      </c>
-      <c r="G29" t="s">
-        <v>512</v>
-      </c>
-      <c r="H29" t="s">
-        <v>515</v>
-      </c>
-      <c r="I29" t="s">
-        <v>563</v>
-      </c>
-      <c r="J29" t="s">
-        <v>517</v>
-      </c>
-      <c r="K29" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>564</v>
-      </c>
-      <c r="B30" t="s">
-        <v>565</v>
-      </c>
-      <c r="C30" t="s">
-        <v>565</v>
-      </c>
-      <c r="D30" t="s">
-        <v>269</v>
-      </c>
-      <c r="E30" t="s">
-        <v>514</v>
-      </c>
-      <c r="F30" t="s">
-        <v>267</v>
-      </c>
-      <c r="G30" t="s">
-        <v>512</v>
-      </c>
-      <c r="H30" t="s">
-        <v>515</v>
-      </c>
-      <c r="I30" t="s">
-        <v>566</v>
-      </c>
-      <c r="J30" t="s">
-        <v>517</v>
-      </c>
-      <c r="K30" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>567</v>
-      </c>
-      <c r="B31" t="s">
-        <v>568</v>
-      </c>
-      <c r="C31" t="s">
-        <v>568</v>
-      </c>
-      <c r="D31" t="s">
-        <v>269</v>
-      </c>
-      <c r="E31" t="s">
-        <v>514</v>
-      </c>
-      <c r="F31" t="s">
-        <v>267</v>
-      </c>
-      <c r="G31" t="s">
-        <v>512</v>
-      </c>
-      <c r="H31" t="s">
-        <v>515</v>
-      </c>
-      <c r="I31" t="s">
-        <v>569</v>
-      </c>
-      <c r="J31" t="s">
-        <v>517</v>
-      </c>
-      <c r="K31" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" t="s">
-        <v>570</v>
-      </c>
-      <c r="B32" t="s">
-        <v>571</v>
-      </c>
-      <c r="C32" t="s">
-        <v>571</v>
-      </c>
-      <c r="D32" t="s">
-        <v>269</v>
-      </c>
-      <c r="E32" t="s">
-        <v>514</v>
-      </c>
-      <c r="F32" t="s">
-        <v>267</v>
-      </c>
-      <c r="G32" t="s">
-        <v>512</v>
-      </c>
-      <c r="H32" t="s">
-        <v>515</v>
-      </c>
-      <c r="I32" t="s">
-        <v>572</v>
-      </c>
-      <c r="J32" t="s">
-        <v>517</v>
-      </c>
-      <c r="K32" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
-        <v>573</v>
-      </c>
-      <c r="B33" t="s">
-        <v>574</v>
-      </c>
-      <c r="C33" t="s">
-        <v>574</v>
-      </c>
-      <c r="D33" t="s">
-        <v>269</v>
-      </c>
-      <c r="E33" t="s">
-        <v>514</v>
-      </c>
-      <c r="F33" t="s">
-        <v>267</v>
-      </c>
-      <c r="G33" t="s">
-        <v>512</v>
-      </c>
-      <c r="H33" t="s">
-        <v>515</v>
-      </c>
-      <c r="I33" t="s">
-        <v>575</v>
-      </c>
-      <c r="J33" t="s">
-        <v>517</v>
-      </c>
-      <c r="K33" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>576</v>
-      </c>
-      <c r="B34" t="s">
-        <v>577</v>
-      </c>
-      <c r="C34" t="s">
-        <v>577</v>
-      </c>
-      <c r="D34" t="s">
-        <v>269</v>
-      </c>
-      <c r="E34" t="s">
-        <v>514</v>
-      </c>
-      <c r="F34" t="s">
-        <v>267</v>
-      </c>
-      <c r="G34" t="s">
-        <v>512</v>
-      </c>
-      <c r="H34" t="s">
-        <v>515</v>
-      </c>
-      <c r="I34" t="s">
-        <v>578</v>
-      </c>
-      <c r="J34" t="s">
-        <v>517</v>
-      </c>
-      <c r="K34" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" t="s">
-        <v>579</v>
-      </c>
-      <c r="B35" t="s">
-        <v>580</v>
-      </c>
-      <c r="C35" t="s">
-        <v>580</v>
-      </c>
-      <c r="D35" t="s">
-        <v>269</v>
-      </c>
-      <c r="E35" t="s">
-        <v>514</v>
-      </c>
-      <c r="F35" t="s">
-        <v>267</v>
-      </c>
-      <c r="G35" t="s">
-        <v>512</v>
-      </c>
-      <c r="H35" t="s">
-        <v>515</v>
-      </c>
-      <c r="I35" t="s">
-        <v>581</v>
-      </c>
-      <c r="J35" t="s">
-        <v>517</v>
-      </c>
-      <c r="K35" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>255</v>
-      </c>
-      <c r="B36" t="s">
-        <v>527</v>
-      </c>
-      <c r="C36" t="s">
-        <v>528</v>
-      </c>
-      <c r="D36" t="s">
-        <v>517</v>
-      </c>
-      <c r="E36" t="s">
-        <v>517</v>
-      </c>
-      <c r="F36" t="s">
-        <v>517</v>
-      </c>
-      <c r="G36" t="s">
-        <v>517</v>
-      </c>
-      <c r="H36" t="s">
-        <v>517</v>
-      </c>
-      <c r="I36" t="s">
-        <v>517</v>
-      </c>
-      <c r="J36" t="s">
-        <v>517</v>
-      </c>
-      <c r="K36" t="s">
-        <v>517</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6639,7 +6236,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6655,11 +6252,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -6669,12 +6261,12 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6684,380 +6276,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>503</v>
+        <v>536</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>583</v>
+        <v>537</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>441</v>
+        <v>538</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B5" t="s">
-        <v>587</v>
-      </c>
-      <c r="C5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D5" t="s">
-        <v>350</v>
-      </c>
-      <c r="E5" t="s">
-        <v>458</v>
-      </c>
-      <c r="F5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>589</v>
-      </c>
-      <c r="B6" t="s">
-        <v>590</v>
-      </c>
-      <c r="C6" t="s">
-        <v>326</v>
-      </c>
-      <c r="D6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E6" t="s">
-        <v>458</v>
-      </c>
-      <c r="F6" t="s">
-        <v>588</v>
-      </c>
-      <c r="G6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>591</v>
-      </c>
-      <c r="B7" t="s">
-        <v>592</v>
-      </c>
-      <c r="C7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" t="s">
-        <v>458</v>
-      </c>
-      <c r="F7" t="s">
-        <v>588</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>593</v>
-      </c>
-      <c r="B8" t="s">
-        <v>594</v>
-      </c>
-      <c r="C8" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E8" t="s">
-        <v>458</v>
-      </c>
-      <c r="F8" t="s">
-        <v>588</v>
-      </c>
-      <c r="G8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>444</v>
-      </c>
-      <c r="B9" t="s">
-        <v>595</v>
-      </c>
-      <c r="C9" t="s">
-        <v>326</v>
-      </c>
-      <c r="D9" t="s">
-        <v>332</v>
-      </c>
-      <c r="E9" t="s">
-        <v>445</v>
-      </c>
-      <c r="F9" t="s">
-        <v>596</v>
-      </c>
-      <c r="G9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H9" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>446</v>
-      </c>
-      <c r="B10" t="s">
-        <v>598</v>
-      </c>
-      <c r="C10" t="s">
-        <v>326</v>
-      </c>
-      <c r="D10" t="s">
-        <v>334</v>
-      </c>
-      <c r="E10" t="s">
-        <v>445</v>
-      </c>
-      <c r="F10" t="s">
-        <v>596</v>
-      </c>
-      <c r="G10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H10" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>447</v>
-      </c>
-      <c r="B11" t="s">
-        <v>600</v>
-      </c>
-      <c r="C11" t="s">
-        <v>326</v>
-      </c>
-      <c r="D11" t="s">
-        <v>336</v>
-      </c>
-      <c r="E11" t="s">
-        <v>445</v>
-      </c>
-      <c r="F11" t="s">
-        <v>596</v>
-      </c>
-      <c r="G11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H11" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>448</v>
-      </c>
-      <c r="B12" t="s">
-        <v>602</v>
-      </c>
-      <c r="C12" t="s">
-        <v>326</v>
-      </c>
-      <c r="D12" t="s">
-        <v>341</v>
-      </c>
-      <c r="E12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F12" t="s">
-        <v>588</v>
-      </c>
-      <c r="G12" t="s">
-        <v>201</v>
-      </c>
-      <c r="H12" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>449</v>
-      </c>
-      <c r="B13" t="s">
-        <v>604</v>
-      </c>
-      <c r="C13" t="s">
-        <v>326</v>
-      </c>
-      <c r="D13" t="s">
-        <v>343</v>
-      </c>
-      <c r="E13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F13" t="s">
-        <v>605</v>
-      </c>
-      <c r="G13" t="s">
-        <v>201</v>
-      </c>
-      <c r="H13" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>449</v>
-      </c>
-      <c r="B14" t="s">
-        <v>604</v>
-      </c>
-      <c r="C14" t="s">
-        <v>326</v>
-      </c>
-      <c r="D14" t="s">
-        <v>345</v>
-      </c>
-      <c r="E14" t="s">
-        <v>445</v>
-      </c>
-      <c r="F14" t="s">
-        <v>605</v>
-      </c>
-      <c r="G14" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>450</v>
-      </c>
-      <c r="B15" t="s">
-        <v>608</v>
-      </c>
-      <c r="C15" t="s">
-        <v>326</v>
-      </c>
-      <c r="D15" t="s">
-        <v>347</v>
-      </c>
-      <c r="E15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F15" t="s">
-        <v>596</v>
-      </c>
-      <c r="G15" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B16" t="s">
-        <v>610</v>
-      </c>
-      <c r="C16" t="s">
-        <v>326</v>
-      </c>
-      <c r="D16" t="s">
-        <v>349</v>
-      </c>
-      <c r="E16" t="s">
-        <v>445</v>
-      </c>
-      <c r="F16" t="s">
-        <v>596</v>
-      </c>
-      <c r="G16" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>452</v>
-      </c>
-      <c r="B17" t="s">
-        <v>612</v>
-      </c>
-      <c r="C17" t="s">
-        <v>326</v>
-      </c>
-      <c r="D17" t="s">
-        <v>453</v>
-      </c>
-      <c r="E17" t="s">
-        <v>445</v>
-      </c>
-      <c r="F17" t="s">
-        <v>596</v>
-      </c>
-      <c r="G17" t="s">
-        <v>201</v>
-      </c>
-      <c r="H17" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>454</v>
-      </c>
-      <c r="B18" t="s">
-        <v>614</v>
-      </c>
-      <c r="C18" t="s">
-        <v>326</v>
-      </c>
-      <c r="D18" t="s">
-        <v>455</v>
-      </c>
-      <c r="E18" t="s">
-        <v>445</v>
-      </c>
-      <c r="F18" t="s">
-        <v>615</v>
-      </c>
-      <c r="G18" t="s">
-        <v>201</v>
-      </c>
-      <c r="H18" t="s">
-        <v>616</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -7067,303 +6307,49 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>502</v>
+        <v>459</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>583</v>
+        <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>584</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>618</v>
+        <v>556</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>619</v>
+        <v>539</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>503</v>
+        <v>553</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>444</v>
-      </c>
-      <c r="B5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D5" t="s">
-        <v>596</v>
-      </c>
-      <c r="E5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" t="s">
-        <v>445</v>
-      </c>
-      <c r="G5" t="s">
-        <v>621</v>
-      </c>
-      <c r="H5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" t="s">
-        <v>596</v>
-      </c>
-      <c r="E6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" t="s">
-        <v>445</v>
-      </c>
-      <c r="G6" t="s">
-        <v>623</v>
-      </c>
-      <c r="H6" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>447</v>
-      </c>
-      <c r="B7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D7" t="s">
-        <v>596</v>
-      </c>
-      <c r="E7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" t="s">
-        <v>445</v>
-      </c>
-      <c r="G7" t="s">
-        <v>625</v>
-      </c>
-      <c r="H7" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>448</v>
-      </c>
-      <c r="B8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" t="s">
-        <v>588</v>
-      </c>
-      <c r="E8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G8" t="s">
-        <v>627</v>
-      </c>
-      <c r="H8" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>449</v>
-      </c>
-      <c r="B9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" t="s">
-        <v>605</v>
-      </c>
-      <c r="E9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" t="s">
-        <v>445</v>
-      </c>
-      <c r="G9" t="s">
-        <v>629</v>
-      </c>
-      <c r="H9" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>449</v>
-      </c>
-      <c r="B10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" t="s">
-        <v>605</v>
-      </c>
-      <c r="E10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" t="s">
-        <v>445</v>
-      </c>
-      <c r="G10" t="s">
-        <v>629</v>
-      </c>
-      <c r="H10" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>450</v>
-      </c>
-      <c r="B11" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" t="s">
-        <v>347</v>
-      </c>
-      <c r="D11" t="s">
-        <v>596</v>
-      </c>
-      <c r="E11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" t="s">
-        <v>445</v>
-      </c>
-      <c r="G11" t="s">
-        <v>631</v>
-      </c>
-      <c r="H11" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>451</v>
-      </c>
-      <c r="B12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" t="s">
-        <v>349</v>
-      </c>
-      <c r="D12" t="s">
-        <v>596</v>
-      </c>
-      <c r="E12" t="s">
-        <v>201</v>
-      </c>
-      <c r="F12" t="s">
-        <v>445</v>
-      </c>
-      <c r="G12" t="s">
-        <v>633</v>
-      </c>
-      <c r="H12" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>452</v>
-      </c>
-      <c r="B13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D13" t="s">
-        <v>596</v>
-      </c>
-      <c r="E13" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13" t="s">
-        <v>445</v>
-      </c>
-      <c r="G13" t="s">
-        <v>635</v>
-      </c>
-      <c r="H13" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>454</v>
-      </c>
-      <c r="B14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" t="s">
-        <v>455</v>
-      </c>
-      <c r="D14" t="s">
-        <v>615</v>
-      </c>
-      <c r="E14" t="s">
-        <v>201</v>
-      </c>
-      <c r="F14" t="s">
-        <v>445</v>
-      </c>
-      <c r="G14" t="s">
-        <v>637</v>
-      </c>
-      <c r="H14" t="s">
-        <v>638</v>
+        <v>467</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -7378,44 +6364,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>639</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>640</v>
+        <v>556</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>441</v>
+        <v>539</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>618</v>
+        <v>552</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>619</v>
+        <v>553</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>511</v>
+        <v>467</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>641</v>
+        <v>557</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>620</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -7425,49 +6411,27 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>620</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -7482,22 +6446,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>643</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>644</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>645</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -7507,27 +6471,12 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>646</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -7537,12 +6486,32 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>648</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -7552,32 +6521,12 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -7592,7 +6541,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>651</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -7602,12 +6551,27 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -7617,12 +6581,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7632,137 +6596,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -7772,27 +6606,17 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>650</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -7807,12 +6631,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -7822,32 +6646,12 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>656</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7862,127 +6666,127 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>657</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>658</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>659</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>660</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>661</v>
+        <v>577</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>662</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>663</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>664</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>665</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>666</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>667</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>668</v>
+        <v>584</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>669</v>
+        <v>585</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>670</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>671</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>672</v>
+        <v>588</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>673</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>674</v>
+        <v>590</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>675</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>676</v>
+        <v>592</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>677</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>678</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>679</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>680</v>
+        <v>596</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>681</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -7997,7 +6801,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8007,7 +6811,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -8022,7 +6826,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8032,7 +6836,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -8042,12 +6846,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8057,102 +6861,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -8162,42 +6886,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -8207,42 +6911,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Sanity.xlsx
+++ b/GREENBANK0_301A/project/Sanity.xlsx
@@ -1801,10 +1801,10 @@
     <t>Pad Connections to Nestos</t>
   </si>
   <si>
-    <t>pad_GREENBANK0_301A_LDO0.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
-  </si>
-  <si>
-    <t>pad_GREENBANK0_301A_LDO1.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+    <t>pad_GREENBANK0_301A_LDO0.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+  </si>
+  <si>
+    <t>pad_GREENBANK0_301A_LDO1.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
   </si>
   <si>
     <t>pad_GREENBANK0_301A_LDO10.LDO10 0.3V -0.3V connects to XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.LDO 6V -0.3V</t>
@@ -1828,25 +1828,25 @@
     <t>pad_GREENBANK0_301A_LDO2.sense_LDO2 0.3V -0.3V connects to XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.INN 6V -0.3V</t>
   </si>
   <si>
-    <t>pad_GREENBANK0_301A_LDO3.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
-  </si>
-  <si>
-    <t>pad_GREENBANK0_301A_LDO4.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+    <t>pad_GREENBANK0_301A_LDO3.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+  </si>
+  <si>
+    <t>pad_GREENBANK0_301A_LDO4.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
   </si>
   <si>
     <t>pad_GREENBANK0_301A_LDO5.sense_LDO5 0.3V -0.3V connects to XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.INN 6V -0.3V</t>
   </si>
   <si>
-    <t>pad_GREENBANK0_301A_LDO6.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+    <t>pad_GREENBANK0_301A_LDO6.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
   </si>
   <si>
     <t>pad_GREENBANK0_301A_LDO7.sense_LDO7 0.3V -0.3V connects to XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.INN 6V -0.3V</t>
   </si>
   <si>
-    <t>pad_GREENBANK0_301A_LDO8.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
-  </si>
-  <si>
-    <t>pad_GREENBANK0_301A_LDO9.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+    <t>pad_GREENBANK0_301A_LDO8.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
+  </si>
+  <si>
+    <t>pad_GREENBANK0_301A_LDO9.MUDV 0.3V -0.3V connects to XU1,XceleraCORE,XSERVICE,XU2.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU4.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU7.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XU9.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU10.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU14.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU17.CELV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU19.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XSERVICE,XU27.SIMPV 6V 2.1V --&gt; XU1,XceleraCORE,XSERVICE,XBYPASS,Xoscillator1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU19,XLDOconfigNO1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOFIXED1,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU19,XLDOUNITY,XLDO1.SIMPV 6V 2.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENhigh,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENlow,Xamplifier1.SIMPV 6V 2.0V --&gt; XU1,XceleraCORE,XU20,XAMPOPENmedium,Xamplifier1.SIMPV 6V 2.0V</t>
   </si>
   <si>
     <t>pad_GREENBANK0_301A_MUDG.kelvin_MUDGamplifier 6V -0.3V connects to XU1,XceleraCORE,XU20,XAMPCONTROLhigh,Xamplifier1.INN 6V -0.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLlow,Xamplifier1.INN 6V -0.3V --&gt; XU1,XceleraCORE,XU20,XAMPCONTROLmedium,Xamplifier1.INN 6V -0.3V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDlow,Xamplifier1.INN 6V -0.3V --&gt; XU1,XceleraCORE,XU20,XAMPFIXEDmedium,Xamplifier1.INN 6V -0.3V</t>

--- a/GREENBANK0_301A/project/Sanity.xlsx
+++ b/GREENBANK0_301A/project/Sanity.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="688">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -231,30 +231,6 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
     <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
@@ -271,6 +247,9 @@
   </si>
   <si>
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>tmi - {"path": "XU1,XceleraCORE", "instance": "XceleraCORE", "symbol": "tmi", "io": "inout", "bus": "[4:0]", "type": "child"}</t>
   </si>
   <si>
     <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
@@ -508,21 +487,57 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 18, 'efficiency': '71.9%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 17, 'efficiency': '73.4%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 5, 'efficiency': '68.8%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
+  </si>
+  <si>
+    <t>{'name': 'drm32', 'bits': 32, 'noconns': 8, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
+  </si>
+  <si>
+    <t>{'name': 'drm32', 'bits': 32, 'noconns': 11, 'efficiency': '65.6%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
+    <t>{'cells': 9, 'bytes': 42.0, 'noconns': 100, 'efficiency': '70.2%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>DFM Efficiency Summary</t>
+  </si>
+  <si>
     <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>DFM Efficiency Summary</t>
-  </si>
-  <si>
     <t>Project Summary</t>
   </si>
   <si>
@@ -1294,6 +1309,54 @@
     <t>1</t>
   </si>
   <si>
+    <t>drm_hex0x01</t>
+  </si>
+  <si>
+    <t>drm64</t>
+  </si>
+  <si>
+    <t>drm_hex0x02</t>
+  </si>
+  <si>
+    <t>drm_hex0x03</t>
+  </si>
+  <si>
+    <t>drm16</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>drm_hex0x04</t>
+  </si>
+  <si>
+    <t>drm32</t>
+  </si>
+  <si>
+    <t>drm_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>drm_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>drm_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>drm_hex0x08</t>
+  </si>
+  <si>
+    <t>drm_hex0x09</t>
+  </si>
+  <si>
     <t>DRM to Memory Check</t>
   </si>
   <si>
@@ -1303,6 +1366,9 @@
     <t>Allowed &lt;= 61</t>
   </si>
   <si>
+    <t>51.0</t>
+  </si>
+  <si>
     <t>61</t>
   </si>
   <si>
@@ -1327,285 +1393,282 @@
     <t>238</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>inv</t>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>nand2</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>PEBBLEtielo</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>switchgnd</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>drmmodule</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>amplifier</t>
+  </si>
+  <si>
+    <t>IPOTTldo</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>nor3</t>
+  </si>
+  <si>
+    <t>ESDminiClamp6</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>currentgenerator</t>
+  </si>
+  <si>
+    <t>celeranoconn</t>
+  </si>
+  <si>
+    <t>switchtransmission</t>
+  </si>
+  <si>
+    <t>porb</t>
+  </si>
+  <si>
+    <t>oscillatorcrude</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>decoder3</t>
+  </si>
+  <si>
+    <t>amux8</t>
+  </si>
+  <si>
+    <t>amux2</t>
+  </si>
+  <si>
+    <t>PAD REPORT</t>
+  </si>
+  <si>
+    <t>Package TQFN3255</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Abs Min</t>
+  </si>
+  <si>
+    <t>Wrt Min</t>
+  </si>
+  <si>
+    <t>Abs Max</t>
+  </si>
+  <si>
+    <t>Wrt Max</t>
+  </si>
+  <si>
+    <t>ESD Rating</t>
+  </si>
+  <si>
+    <t>ESD Connect</t>
+  </si>
+  <si>
+    <t>Imax</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>MUDV</t>
+  </si>
+  <si>
+    <t>Supply</t>
+  </si>
+  <si>
+    <t>MUDG</t>
+  </si>
+  <si>
+    <t>2KV</t>
+  </si>
+  <si>
+    <t>ESDcore6 MUDV -&gt; GESD &amp; ESDcore6 CELPOWER_LDO -&gt; GESD</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>CELINA</t>
+  </si>
+  <si>
+    <t>DFT analog input testmode pad (Connect to GND)</t>
+  </si>
+  <si>
+    <t>ESDcore6 CELINA -&gt; GESD</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>No Connect</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>LDO15</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO15 &amp; ESDdiode LDO15 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>LDO14</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO14 &amp; ESDdiode LDO14 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>LDO13</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO13 &amp; ESDdiode LDO13 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>LDO12</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO12 &amp; ESDdiode LDO12 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>LDO11</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO11 &amp; ESDdiode LDO11 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>LDO10</t>
+  </si>
+  <si>
+    <t>Data1</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO10 &amp; ESDdiode LDO10 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>LDO9</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO9 &amp; ESDdiode LDO9 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>LDO8</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO8 &amp; ESDdiode LDO8 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>LDO7</t>
+  </si>
+  <si>
+    <t>ESDdiode MUDV -&gt; LDO7 &amp; ESDdiode LDO7 -&gt; GESD</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>switchgnd</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>amplifier</t>
-  </si>
-  <si>
-    <t>IPOTTldo</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
-    <t>capacitorfixed</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
-    <t>nor3</t>
-  </si>
-  <si>
-    <t>ESDminiClamp6</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>currentgenerator</t>
-  </si>
-  <si>
-    <t>celeranoconn</t>
-  </si>
-  <si>
-    <t>switchtransmission</t>
-  </si>
-  <si>
-    <t>porb</t>
-  </si>
-  <si>
-    <t>oscillatorcrude</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>decoder3</t>
-  </si>
-  <si>
-    <t>amux8</t>
-  </si>
-  <si>
-    <t>amux2</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
-  </si>
-  <si>
-    <t>PAD REPORT</t>
-  </si>
-  <si>
-    <t>Package TQFN3255</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Abs Min</t>
-  </si>
-  <si>
-    <t>Wrt Min</t>
-  </si>
-  <si>
-    <t>Abs Max</t>
-  </si>
-  <si>
-    <t>Wrt Max</t>
-  </si>
-  <si>
-    <t>ESD Rating</t>
-  </si>
-  <si>
-    <t>ESD Connect</t>
-  </si>
-  <si>
-    <t>Imax</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>MUDV</t>
-  </si>
-  <si>
-    <t>Supply</t>
-  </si>
-  <si>
-    <t>MUDG</t>
-  </si>
-  <si>
-    <t>2KV</t>
-  </si>
-  <si>
-    <t>ESDcore6 MUDV -&gt; GESD &amp; ESDcore6 CELPOWER_LDO -&gt; GESD</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>CELINA</t>
-  </si>
-  <si>
-    <t>DFT analog input testmode pad (Connect to GND)</t>
-  </si>
-  <si>
-    <t>ESDcore6 CELINA -&gt; GESD</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>No Connect</t>
-  </si>
-  <si>
-    <t>Ground</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>LDO15</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO15 &amp; ESDdiode LDO15 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>LDO14</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO14 &amp; ESDdiode LDO14 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>LDO13</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO13 &amp; ESDdiode LDO13 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>LDO12</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO12 &amp; ESDdiode LDO12 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>LDO11</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO11 &amp; ESDdiode LDO11 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>LDO10</t>
-  </si>
-  <si>
-    <t>Data1</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO10 &amp; ESDdiode LDO10 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>LDO9</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO9 &amp; ESDdiode LDO9 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>LDO8</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO8 &amp; ESDdiode LDO8 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>LDO7</t>
-  </si>
-  <si>
-    <t>ESDdiode MUDV -&gt; LDO7 &amp; ESDdiode LDO7 -&gt; GESD</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>LDO6</t>
   </si>
   <si>
@@ -1735,7 +1798,214 @@
     <t>path</t>
   </si>
   <si>
+    <t>Reference5_Curvature_Correction_Accuracy</t>
+  </si>
+  <si>
+    <t>REFERENCE5curve</t>
+  </si>
+  <si>
+    <t>4:0</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XSERVICE,drm_hex0x01</t>
+  </si>
+  <si>
+    <t>{'nesto': 'reference_d628bb93', 'fields': [{'desc': 'REFERENCE5curve', 'name': 'REFERENCE5curve', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>Reference4_Curvature_Correction_Accuracy</t>
+  </si>
+  <si>
+    <t>REFERENCE4curve</t>
+  </si>
+  <si>
+    <t>{'nesto': 'reference_0c0fda20', 'fields': [{'desc': 'REFERENCE4curve', 'name': 'REFERENCE4curve', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>Reference1_Curvature_Correction_Accuracy</t>
+  </si>
+  <si>
+    <t>REFERENCE1curve</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XSERVICE,drm_hex0x02</t>
+  </si>
+  <si>
+    <t>{'nesto': 'reference_c03501a6', 'fields': [{'desc': 'REFERENCE1curve', 'name': 'REFERENCE1curve', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>Reference0_Curvature_Correction_Accuracy</t>
+  </si>
+  <si>
+    <t>REFERENCE0curve</t>
+  </si>
+  <si>
+    <t>{'nesto': 'reference_425caed2', 'fields': [{'desc': 'REFERENCE0curve', 'name': 'REFERENCE0curve', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XSERVICE,drm_hex0x03</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>factory_ldogain</t>
+  </si>
+  <si>
+    <t>2:0</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1,drm_hex0x04</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_d90fb091', 'fields': [{'desc': 'factory_ldogain', 'name': 'factory_ldogain', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>factory_ldoerror</t>
+  </si>
+  <si>
+    <t>5:3</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_d90fb091', 'fields': [{'desc': 'factory_ldoerror', 'name': 'factory_ldoerror', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>factory_ldopsrr</t>
+  </si>
+  <si>
+    <t>5:0</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_d90fb091', 'fields': [{'desc': 'factory_ldopsrr', 'name': 'factory_ldopsrr', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>factory_ldooutput</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_d90fb091', 'fields': [{'desc': 'factory_ldooutput', 'name': 'factory_ldooutput', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>factory_ldofeedforward</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_d90fb091', 'fields': [{'desc': 'factory_ldofeedforward', 'name': 'factory_ldofeedforward', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>factory_ldocompensation</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_d90fb091', 'fields': [{'desc': 'factory_ldocompensation', 'name': 'factory_ldocompensation', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,drm_hex0x05</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_76e6366b', 'fields': [{'desc': 'factory_ldogain', 'name': 'factory_ldogain', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_76e6366b', 'fields': [{'desc': 'factory_ldoerror', 'name': 'factory_ldoerror', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_76e6366b', 'fields': [{'desc': 'factory_ldopsrr', 'name': 'factory_ldopsrr', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_76e6366b', 'fields': [{'desc': 'factory_ldooutput', 'name': 'factory_ldooutput', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_76e6366b', 'fields': [{'desc': 'factory_ldofeedforward', 'name': 'factory_ldofeedforward', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_76e6366b', 'fields': [{'desc': 'factory_ldocompensation', 'name': 'factory_ldocompensation', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED1,drm_hex0x06</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_aec3f94a', 'fields': [{'desc': 'factory_ldogain', 'name': 'factory_ldogain', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_aec3f94a', 'fields': [{'desc': 'factory_ldoerror', 'name': 'factory_ldoerror', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_aec3f94a', 'fields': [{'desc': 'factory_ldopsrr', 'name': 'factory_ldopsrr', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_aec3f94a', 'fields': [{'desc': 'factory_ldofeedforward', 'name': 'factory_ldofeedforward', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_aec3f94a', 'fields': [{'desc': 'factory_ldocompensation', 'name': 'factory_ldocompensation', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE,drm_hex0x07</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_f73e41d5', 'fields': [{'desc': 'factory_ldogain', 'name': 'factory_ldogain', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_f73e41d5', 'fields': [{'desc': 'factory_ldoerror', 'name': 'factory_ldoerror', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_f73e41d5', 'fields': [{'desc': 'factory_ldopsrr', 'name': 'factory_ldopsrr', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_f73e41d5', 'fields': [{'desc': 'factory_ldofeedforward', 'name': 'factory_ldofeedforward', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_f73e41d5', 'fields': [{'desc': 'factory_ldocompensation', 'name': 'factory_ldocompensation', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA,drm_hex0x08</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_2e36c35f', 'fields': [{'desc': 'factory_ldogain', 'name': 'factory_ldogain', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_2e36c35f', 'fields': [{'desc': 'factory_ldoerror', 'name': 'factory_ldoerror', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_2e36c35f', 'fields': [{'desc': 'factory_ldopsrr', 'name': 'factory_ldopsrr', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_2e36c35f', 'fields': [{'desc': 'factory_ldofeedforward', 'name': 'factory_ldofeedforward', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_2e36c35f', 'fields': [{'desc': 'factory_ldocompensation', 'name': 'factory_ldocompensation', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOUNITY,drm_hex0x09</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_cb30dffd', 'fields': [{'desc': 'factory_ldogain', 'name': 'factory_ldogain', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_cb30dffd', 'fields': [{'desc': 'factory_ldoerror', 'name': 'factory_ldoerror', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_cb30dffd', 'fields': [{'desc': 'factory_ldopsrr', 'name': 'factory_ldopsrr', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_cb30dffd', 'fields': [{'desc': 'factory_ldofeedforward', 'name': 'factory_ldofeedforward', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'IPOTTldo_cb30dffd', 'fields': [{'desc': 'factory_ldocompensation', 'name': 'factory_ldocompensation', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
     <t>ACCURACY ADDRESS REPORT</t>
+  </si>
+  <si>
+    <t>6:0</t>
+  </si>
+  <si>
+    <t>REFERENCE2_accuracy_0p8V</t>
+  </si>
+  <si>
+    <t>REFERENCE2accuracy</t>
+  </si>
+  <si>
+    <t>{'nesto': 'currentgenerator_25ffd7d0', 'fields': [{'desc': 'REFERENCE2accuracy', 'name': 'REFERENCE2accuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
+  </si>
+  <si>
+    <t>{'nesto': 'currentgenerator_94421a49', 'fields': [{'desc': 'REFERENCE2accuracy', 'name': 'REFERENCE2accuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
   </si>
   <si>
     <t>DFT PROBE ADDRESS REPORT</t>
@@ -2218,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2228,92 +2498,57 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2328,7 +2563,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2348,7 +2583,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2363,7 +2598,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2378,7 +2613,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2398,12 +2633,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2418,212 +2653,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2638,12 +2873,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2658,7 +2893,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2678,127 +2913,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2808,17 +3043,92 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3078,17 +3388,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3103,7 +3413,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3123,17 +3433,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3148,52 +3458,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3208,81 +3518,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3290,185 +3600,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3476,453 +3786,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B55" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B56" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B67" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B68" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B69" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B70" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B80" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B81" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B90" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B94" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B95" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B96" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B100" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -3930,628 +4240,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B102" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B106" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B107" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B108" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B109" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B110" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B111" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B112" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B113" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B116" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B117" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B118" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B119" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B120" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B121" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B122" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
+        <v>318</v>
+      </c>
+      <c r="B123" t="s">
         <v>313</v>
-      </c>
-      <c r="B123" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B125" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B126" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B127" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B128" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B129" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B130" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B131" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B132" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B133" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B134" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B137" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B138" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B139" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B140" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B141" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B142" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B143" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B144" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B146" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B147" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B148" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B149" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B150" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B151" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B152" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B153" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B154" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B155" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B156" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B157" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B158" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B159" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B160" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B161" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B162" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B163" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B164" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B165" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B166" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B167" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B168" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B169" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B170" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B171" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B172" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B173" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B174" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B175" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B176" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B177" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B178" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B179" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B180" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4561,76 +4871,418 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>411</v>
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J5" t="s">
+        <v>326</v>
+      </c>
+      <c r="K5" t="s">
+        <v>182</v>
+      </c>
+      <c r="L5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>413</v>
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" t="s">
+        <v>326</v>
+      </c>
+      <c r="K6" t="s">
+        <v>182</v>
+      </c>
+      <c r="L6" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>419</v>
+      </c>
+      <c r="C7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F7" t="s">
+        <v>421</v>
+      </c>
+      <c r="G7" t="s">
+        <v>421</v>
+      </c>
+      <c r="H7" t="s">
+        <v>421</v>
+      </c>
+      <c r="I7" t="s">
+        <v>421</v>
+      </c>
+      <c r="J7" t="s">
+        <v>421</v>
+      </c>
+      <c r="K7" t="s">
+        <v>182</v>
+      </c>
+      <c r="L7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E8" t="s">
+        <v>421</v>
+      </c>
+      <c r="F8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H8" t="s">
+        <v>421</v>
+      </c>
+      <c r="I8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8" t="s">
+        <v>182</v>
+      </c>
+      <c r="L8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F9" t="s">
+        <v>421</v>
+      </c>
+      <c r="G9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H9" t="s">
+        <v>421</v>
+      </c>
+      <c r="I9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J9" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" t="s">
+        <v>182</v>
+      </c>
+      <c r="L9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" t="s">
+        <v>421</v>
+      </c>
+      <c r="G10" t="s">
+        <v>421</v>
+      </c>
+      <c r="H10" t="s">
+        <v>421</v>
+      </c>
+      <c r="I10" t="s">
+        <v>182</v>
+      </c>
+      <c r="J10" t="s">
+        <v>182</v>
+      </c>
+      <c r="K10" t="s">
+        <v>182</v>
+      </c>
+      <c r="L10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" t="s">
+        <v>428</v>
+      </c>
+      <c r="C11" t="s">
+        <v>429</v>
+      </c>
+      <c r="D11" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" t="s">
+        <v>421</v>
+      </c>
+      <c r="F11" t="s">
+        <v>421</v>
+      </c>
+      <c r="G11" t="s">
+        <v>421</v>
+      </c>
+      <c r="H11" t="s">
+        <v>421</v>
+      </c>
+      <c r="I11" t="s">
+        <v>182</v>
+      </c>
+      <c r="J11" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" t="s">
+        <v>182</v>
+      </c>
+      <c r="L11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E12" t="s">
+        <v>421</v>
+      </c>
+      <c r="F12" t="s">
+        <v>421</v>
+      </c>
+      <c r="G12" t="s">
+        <v>421</v>
+      </c>
+      <c r="H12" t="s">
+        <v>421</v>
+      </c>
+      <c r="I12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J12" t="s">
+        <v>182</v>
+      </c>
+      <c r="K12" t="s">
+        <v>182</v>
+      </c>
+      <c r="L12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C13" t="s">
+        <v>396</v>
+      </c>
+      <c r="D13" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" t="s">
+        <v>421</v>
+      </c>
+      <c r="F13" t="s">
+        <v>421</v>
+      </c>
+      <c r="G13" t="s">
+        <v>421</v>
+      </c>
+      <c r="H13" t="s">
+        <v>421</v>
+      </c>
+      <c r="I13" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" t="s">
+        <v>182</v>
+      </c>
+      <c r="K13" t="s">
+        <v>182</v>
+      </c>
+      <c r="L13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B16" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -4645,26 +5297,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -4679,7 +5331,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4689,234 +5341,234 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B7" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="B8" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="B9" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="B10" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B11" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="B15" t="s">
-        <v>409</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="B22" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="B23" t="s">
-        <v>410</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="B24" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="B25" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="B26" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="B27" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="B28" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="B29" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="B30" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="B31" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="B32" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -4931,1164 +5583,1164 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B5" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="C5" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E5" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="H5" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I5" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="J5" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K5" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="C6" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E6" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G6" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="H6" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I6" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="J6" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K6" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B7" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C7" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K7" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B8" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C8" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="D8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E8" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G8" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="H8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="J8" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K8" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B9" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C9" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K9" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B10" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C10" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K10" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B11" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C11" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K11" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C12" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K12" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="B13" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C13" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K13" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B14" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C14" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K14" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="B15" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C15" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K15" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B16" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="C16" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="D16" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E16" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F16" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G16" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H16" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I16" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="J16" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K16" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="B17" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="C17" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E17" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F17" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G17" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H17" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I17" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="J17" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K17" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="B18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C18" t="s">
+        <v>512</v>
+      </c>
+      <c r="D18" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" t="s">
+        <v>493</v>
+      </c>
+      <c r="F18" t="s">
+        <v>248</v>
+      </c>
+      <c r="G18" t="s">
         <v>491</v>
       </c>
-      <c r="C18" t="s">
-        <v>491</v>
-      </c>
-      <c r="D18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" t="s">
-        <v>470</v>
-      </c>
-      <c r="F18" t="s">
-        <v>243</v>
-      </c>
-      <c r="G18" t="s">
-        <v>468</v>
-      </c>
       <c r="H18" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I18" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="J18" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K18" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
+        <v>514</v>
+      </c>
+      <c r="B19" t="s">
+        <v>515</v>
+      </c>
+      <c r="C19" t="s">
+        <v>515</v>
+      </c>
+      <c r="D19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" t="s">
         <v>493</v>
       </c>
-      <c r="B19" t="s">
+      <c r="F19" t="s">
+        <v>248</v>
+      </c>
+      <c r="G19" t="s">
+        <v>491</v>
+      </c>
+      <c r="H19" t="s">
         <v>494</v>
       </c>
-      <c r="C19" t="s">
-        <v>494</v>
-      </c>
-      <c r="D19" t="s">
-        <v>245</v>
-      </c>
-      <c r="E19" t="s">
-        <v>470</v>
-      </c>
-      <c r="F19" t="s">
-        <v>243</v>
-      </c>
-      <c r="G19" t="s">
-        <v>468</v>
-      </c>
-      <c r="H19" t="s">
-        <v>471</v>
-      </c>
       <c r="I19" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="J19" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K19" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B20" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C20" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K20" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="B21" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C21" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K21" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="B22" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C22" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K22" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="B23" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="C23" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="D23" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E23" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F23" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G23" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H23" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I23" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="J23" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K23" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="B24" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="C24" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="D24" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E24" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F24" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G24" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H24" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I24" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="J24" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K24" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B25" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="C25" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="D25" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E25" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F25" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G25" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H25" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I25" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="J25" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K25" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="B26" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="C26" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="D26" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E26" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F26" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G26" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H26" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I26" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="J26" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K26" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="B27" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="C27" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E27" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F27" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G27" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H27" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I27" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="J27" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K27" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="B28" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C28" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K28" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>429</v>
+        <v>535</v>
       </c>
       <c r="B29" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="C29" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E29" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F29" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G29" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H29" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I29" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="J29" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K29" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="B30" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="C30" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="D30" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E30" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G30" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H30" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I30" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="J30" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K30" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="B31" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="C31" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="D31" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E31" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F31" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G31" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H31" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I31" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="J31" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K31" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B32" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="C32" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="D32" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E32" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F32" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G32" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H32" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I32" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="J32" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K32" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B33" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="C33" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="D33" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E33" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G33" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H33" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I33" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="J33" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K33" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="B34" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="C34" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="D34" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F34" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G34" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H34" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I34" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="J34" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K34" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="B35" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="C35" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="D35" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E35" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="F35" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G35" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="H35" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="I35" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="J35" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K35" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B36" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C36" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="D36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="E36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="F36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="G36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="H36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="I36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="J36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
       <c r="K36" t="s">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -6103,7 +6755,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6113,94 +6765,94 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="B5" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="C5" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E5" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="F5" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="G5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B6" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E6" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="F6" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="G6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="B7" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="C7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E7" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="F7" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="G7" t="s">
         <v>1</v>
@@ -6208,25 +6860,25 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="B8" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D8" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E8" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="F8" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="G8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -6266,7 +6918,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6276,28 +6928,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -6307,49 +6959,1209 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>554</v>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" t="s">
+        <v>581</v>
+      </c>
+      <c r="G5" t="s">
+        <v>326</v>
+      </c>
+      <c r="I5" t="s">
+        <v>582</v>
+      </c>
+      <c r="J5" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B6" t="s">
+        <v>580</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" t="s">
+        <v>581</v>
+      </c>
+      <c r="G6" t="s">
+        <v>326</v>
+      </c>
+      <c r="I6" t="s">
+        <v>582</v>
+      </c>
+      <c r="J6" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>584</v>
+      </c>
+      <c r="B7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" t="s">
+        <v>581</v>
+      </c>
+      <c r="G7" t="s">
+        <v>326</v>
+      </c>
+      <c r="I7" t="s">
+        <v>582</v>
+      </c>
+      <c r="J7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>584</v>
+      </c>
+      <c r="B8" t="s">
+        <v>585</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" t="s">
+        <v>581</v>
+      </c>
+      <c r="G8" t="s">
+        <v>326</v>
+      </c>
+      <c r="I8" t="s">
+        <v>582</v>
+      </c>
+      <c r="J8" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>587</v>
+      </c>
+      <c r="B9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" t="s">
+        <v>581</v>
+      </c>
+      <c r="G9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I9" t="s">
+        <v>589</v>
+      </c>
+      <c r="J9" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B10" t="s">
+        <v>588</v>
+      </c>
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" t="s">
+        <v>581</v>
+      </c>
+      <c r="G10" t="s">
+        <v>326</v>
+      </c>
+      <c r="I10" t="s">
+        <v>589</v>
+      </c>
+      <c r="J10" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B11" t="s">
+        <v>592</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>413</v>
+      </c>
+      <c r="E11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G11" t="s">
+        <v>326</v>
+      </c>
+      <c r="I11" t="s">
+        <v>589</v>
+      </c>
+      <c r="J11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B12" t="s">
+        <v>592</v>
+      </c>
+      <c r="C12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F12" t="s">
+        <v>581</v>
+      </c>
+      <c r="G12" t="s">
+        <v>326</v>
+      </c>
+      <c r="I12" t="s">
+        <v>594</v>
+      </c>
+      <c r="J12" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>595</v>
+      </c>
+      <c r="B13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>292</v>
+      </c>
+      <c r="F13" t="s">
+        <v>597</v>
+      </c>
+      <c r="G13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13" t="s">
+        <v>598</v>
+      </c>
+      <c r="J13" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>595</v>
+      </c>
+      <c r="B14" t="s">
+        <v>600</v>
+      </c>
+      <c r="C14" t="s">
+        <v>392</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F14" t="s">
+        <v>601</v>
+      </c>
+      <c r="G14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" t="s">
+        <v>598</v>
+      </c>
+      <c r="J14" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>595</v>
+      </c>
+      <c r="B15" t="s">
+        <v>603</v>
+      </c>
+      <c r="C15" t="s">
+        <v>392</v>
+      </c>
+      <c r="D15" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" t="s">
+        <v>604</v>
+      </c>
+      <c r="G15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" t="s">
+        <v>598</v>
+      </c>
+      <c r="J15" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>595</v>
+      </c>
+      <c r="B16" t="s">
+        <v>606</v>
+      </c>
+      <c r="C16" t="s">
+        <v>392</v>
+      </c>
+      <c r="D16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I16" t="s">
+        <v>598</v>
+      </c>
+      <c r="J16" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>595</v>
+      </c>
+      <c r="B17" t="s">
+        <v>608</v>
+      </c>
+      <c r="C17" t="s">
+        <v>392</v>
+      </c>
+      <c r="D17" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" t="s">
+        <v>292</v>
+      </c>
+      <c r="F17" t="s">
+        <v>601</v>
+      </c>
+      <c r="G17" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" t="s">
+        <v>598</v>
+      </c>
+      <c r="J17" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>595</v>
+      </c>
+      <c r="B18" t="s">
+        <v>610</v>
+      </c>
+      <c r="C18" t="s">
+        <v>392</v>
+      </c>
+      <c r="D18" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" t="s">
+        <v>604</v>
+      </c>
+      <c r="G18" t="s">
+        <v>182</v>
+      </c>
+      <c r="I18" t="s">
+        <v>598</v>
+      </c>
+      <c r="J18" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>595</v>
+      </c>
+      <c r="B19" t="s">
+        <v>596</v>
+      </c>
+      <c r="C19" t="s">
+        <v>425</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>292</v>
+      </c>
+      <c r="F19" t="s">
+        <v>597</v>
+      </c>
+      <c r="G19" t="s">
+        <v>182</v>
+      </c>
+      <c r="I19" t="s">
+        <v>612</v>
+      </c>
+      <c r="J19" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" t="s">
+        <v>600</v>
+      </c>
+      <c r="C20" t="s">
+        <v>425</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>292</v>
+      </c>
+      <c r="F20" t="s">
+        <v>601</v>
+      </c>
+      <c r="G20" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" t="s">
+        <v>612</v>
+      </c>
+      <c r="J20" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>595</v>
+      </c>
+      <c r="B21" t="s">
+        <v>603</v>
+      </c>
+      <c r="C21" t="s">
+        <v>425</v>
+      </c>
+      <c r="D21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E21" t="s">
+        <v>208</v>
+      </c>
+      <c r="F21" t="s">
+        <v>604</v>
+      </c>
+      <c r="G21" t="s">
+        <v>182</v>
+      </c>
+      <c r="I21" t="s">
+        <v>612</v>
+      </c>
+      <c r="J21" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>595</v>
+      </c>
+      <c r="B22" t="s">
+        <v>606</v>
+      </c>
+      <c r="C22" t="s">
+        <v>425</v>
+      </c>
+      <c r="D22" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" t="s">
+        <v>292</v>
+      </c>
+      <c r="F22" t="s">
+        <v>597</v>
+      </c>
+      <c r="G22" t="s">
+        <v>182</v>
+      </c>
+      <c r="I22" t="s">
+        <v>612</v>
+      </c>
+      <c r="J22" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>595</v>
+      </c>
+      <c r="B23" t="s">
+        <v>608</v>
+      </c>
+      <c r="C23" t="s">
+        <v>425</v>
+      </c>
+      <c r="D23" t="s">
+        <v>227</v>
+      </c>
+      <c r="E23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F23" t="s">
+        <v>601</v>
+      </c>
+      <c r="G23" t="s">
+        <v>182</v>
+      </c>
+      <c r="I23" t="s">
+        <v>612</v>
+      </c>
+      <c r="J23" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>595</v>
+      </c>
+      <c r="B24" t="s">
+        <v>610</v>
+      </c>
+      <c r="C24" t="s">
+        <v>425</v>
+      </c>
+      <c r="D24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E24" t="s">
+        <v>208</v>
+      </c>
+      <c r="F24" t="s">
+        <v>604</v>
+      </c>
+      <c r="G24" t="s">
+        <v>182</v>
+      </c>
+      <c r="I24" t="s">
+        <v>612</v>
+      </c>
+      <c r="J24" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>595</v>
+      </c>
+      <c r="B25" t="s">
+        <v>596</v>
+      </c>
+      <c r="C25" t="s">
+        <v>427</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F25" t="s">
+        <v>597</v>
+      </c>
+      <c r="G25" t="s">
+        <v>182</v>
+      </c>
+      <c r="I25" t="s">
+        <v>619</v>
+      </c>
+      <c r="J25" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>595</v>
+      </c>
+      <c r="B26" t="s">
+        <v>600</v>
+      </c>
+      <c r="C26" t="s">
+        <v>427</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>292</v>
+      </c>
+      <c r="F26" t="s">
+        <v>601</v>
+      </c>
+      <c r="G26" t="s">
+        <v>182</v>
+      </c>
+      <c r="I26" t="s">
+        <v>619</v>
+      </c>
+      <c r="J26" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>595</v>
+      </c>
+      <c r="B27" t="s">
+        <v>603</v>
+      </c>
+      <c r="C27" t="s">
+        <v>427</v>
+      </c>
+      <c r="D27" t="s">
+        <v>415</v>
+      </c>
+      <c r="E27" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" t="s">
+        <v>604</v>
+      </c>
+      <c r="G27" t="s">
+        <v>182</v>
+      </c>
+      <c r="I27" t="s">
+        <v>619</v>
+      </c>
+      <c r="J27" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>595</v>
+      </c>
+      <c r="B28" t="s">
+        <v>608</v>
+      </c>
+      <c r="C28" t="s">
+        <v>427</v>
+      </c>
+      <c r="D28" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" t="s">
+        <v>292</v>
+      </c>
+      <c r="F28" t="s">
+        <v>597</v>
+      </c>
+      <c r="G28" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" t="s">
+        <v>619</v>
+      </c>
+      <c r="J28" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>595</v>
+      </c>
+      <c r="B29" t="s">
+        <v>610</v>
+      </c>
+      <c r="C29" t="s">
+        <v>427</v>
+      </c>
+      <c r="D29" t="s">
+        <v>292</v>
+      </c>
+      <c r="E29" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" t="s">
+        <v>604</v>
+      </c>
+      <c r="G29" t="s">
+        <v>182</v>
+      </c>
+      <c r="I29" t="s">
+        <v>619</v>
+      </c>
+      <c r="J29" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>595</v>
+      </c>
+      <c r="B30" t="s">
+        <v>596</v>
+      </c>
+      <c r="C30" t="s">
+        <v>429</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>292</v>
+      </c>
+      <c r="F30" t="s">
+        <v>597</v>
+      </c>
+      <c r="G30" t="s">
+        <v>182</v>
+      </c>
+      <c r="I30" t="s">
+        <v>625</v>
+      </c>
+      <c r="J30" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>595</v>
+      </c>
+      <c r="B31" t="s">
+        <v>600</v>
+      </c>
+      <c r="C31" t="s">
+        <v>429</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>292</v>
+      </c>
+      <c r="F31" t="s">
+        <v>601</v>
+      </c>
+      <c r="G31" t="s">
+        <v>182</v>
+      </c>
+      <c r="I31" t="s">
+        <v>625</v>
+      </c>
+      <c r="J31" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>595</v>
+      </c>
+      <c r="B32" t="s">
+        <v>603</v>
+      </c>
+      <c r="C32" t="s">
+        <v>429</v>
+      </c>
+      <c r="D32" t="s">
+        <v>415</v>
+      </c>
+      <c r="E32" t="s">
+        <v>208</v>
+      </c>
+      <c r="F32" t="s">
+        <v>604</v>
+      </c>
+      <c r="G32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I32" t="s">
+        <v>625</v>
+      </c>
+      <c r="J32" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>595</v>
+      </c>
+      <c r="B33" t="s">
+        <v>608</v>
+      </c>
+      <c r="C33" t="s">
+        <v>429</v>
+      </c>
+      <c r="D33" t="s">
+        <v>227</v>
+      </c>
+      <c r="E33" t="s">
+        <v>292</v>
+      </c>
+      <c r="F33" t="s">
+        <v>597</v>
+      </c>
+      <c r="G33" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>595</v>
+      </c>
+      <c r="B34" t="s">
+        <v>610</v>
+      </c>
+      <c r="C34" t="s">
+        <v>429</v>
+      </c>
+      <c r="D34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E34" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" t="s">
+        <v>604</v>
+      </c>
+      <c r="G34" t="s">
+        <v>182</v>
+      </c>
+      <c r="I34" t="s">
+        <v>625</v>
+      </c>
+      <c r="J34" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>595</v>
+      </c>
+      <c r="B35" t="s">
+        <v>596</v>
+      </c>
+      <c r="C35" t="s">
+        <v>394</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>292</v>
+      </c>
+      <c r="F35" t="s">
+        <v>597</v>
+      </c>
+      <c r="G35" t="s">
+        <v>182</v>
+      </c>
+      <c r="I35" t="s">
+        <v>631</v>
+      </c>
+      <c r="J35" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>595</v>
+      </c>
+      <c r="B36" t="s">
+        <v>600</v>
+      </c>
+      <c r="C36" t="s">
+        <v>394</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>292</v>
+      </c>
+      <c r="F36" t="s">
+        <v>601</v>
+      </c>
+      <c r="G36" t="s">
+        <v>182</v>
+      </c>
+      <c r="I36" t="s">
+        <v>631</v>
+      </c>
+      <c r="J36" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>595</v>
+      </c>
+      <c r="B37" t="s">
+        <v>603</v>
+      </c>
+      <c r="C37" t="s">
+        <v>394</v>
+      </c>
+      <c r="D37" t="s">
+        <v>415</v>
+      </c>
+      <c r="E37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" t="s">
+        <v>604</v>
+      </c>
+      <c r="G37" t="s">
+        <v>182</v>
+      </c>
+      <c r="I37" t="s">
+        <v>631</v>
+      </c>
+      <c r="J37" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>595</v>
+      </c>
+      <c r="B38" t="s">
+        <v>608</v>
+      </c>
+      <c r="C38" t="s">
+        <v>394</v>
+      </c>
+      <c r="D38" t="s">
+        <v>227</v>
+      </c>
+      <c r="E38" t="s">
+        <v>292</v>
+      </c>
+      <c r="F38" t="s">
+        <v>597</v>
+      </c>
+      <c r="G38" t="s">
+        <v>182</v>
+      </c>
+      <c r="I38" t="s">
+        <v>631</v>
+      </c>
+      <c r="J38" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>595</v>
+      </c>
+      <c r="B39" t="s">
+        <v>610</v>
+      </c>
+      <c r="C39" t="s">
+        <v>394</v>
+      </c>
+      <c r="D39" t="s">
+        <v>292</v>
+      </c>
+      <c r="E39" t="s">
+        <v>208</v>
+      </c>
+      <c r="F39" t="s">
+        <v>604</v>
+      </c>
+      <c r="G39" t="s">
+        <v>182</v>
+      </c>
+      <c r="I39" t="s">
+        <v>631</v>
+      </c>
+      <c r="J39" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>595</v>
+      </c>
+      <c r="B40" t="s">
+        <v>596</v>
+      </c>
+      <c r="C40" t="s">
+        <v>396</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>292</v>
+      </c>
+      <c r="F40" t="s">
+        <v>597</v>
+      </c>
+      <c r="G40" t="s">
+        <v>182</v>
+      </c>
+      <c r="I40" t="s">
+        <v>637</v>
+      </c>
+      <c r="J40" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>595</v>
+      </c>
+      <c r="B41" t="s">
+        <v>600</v>
+      </c>
+      <c r="C41" t="s">
+        <v>396</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>292</v>
+      </c>
+      <c r="F41" t="s">
+        <v>601</v>
+      </c>
+      <c r="G41" t="s">
+        <v>182</v>
+      </c>
+      <c r="I41" t="s">
+        <v>637</v>
+      </c>
+      <c r="J41" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>595</v>
+      </c>
+      <c r="B42" t="s">
+        <v>603</v>
+      </c>
+      <c r="C42" t="s">
+        <v>396</v>
+      </c>
+      <c r="D42" t="s">
+        <v>415</v>
+      </c>
+      <c r="E42" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" t="s">
+        <v>604</v>
+      </c>
+      <c r="G42" t="s">
+        <v>182</v>
+      </c>
+      <c r="I42" t="s">
+        <v>637</v>
+      </c>
+      <c r="J42" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>595</v>
+      </c>
+      <c r="B43" t="s">
+        <v>608</v>
+      </c>
+      <c r="C43" t="s">
+        <v>396</v>
+      </c>
+      <c r="D43" t="s">
+        <v>227</v>
+      </c>
+      <c r="E43" t="s">
+        <v>292</v>
+      </c>
+      <c r="F43" t="s">
+        <v>597</v>
+      </c>
+      <c r="G43" t="s">
+        <v>182</v>
+      </c>
+      <c r="I43" t="s">
+        <v>637</v>
+      </c>
+      <c r="J43" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>595</v>
+      </c>
+      <c r="B44" t="s">
+        <v>610</v>
+      </c>
+      <c r="C44" t="s">
+        <v>396</v>
+      </c>
+      <c r="D44" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" t="s">
+        <v>208</v>
+      </c>
+      <c r="F44" t="s">
+        <v>604</v>
+      </c>
+      <c r="G44" t="s">
+        <v>182</v>
+      </c>
+      <c r="I44" t="s">
+        <v>637</v>
+      </c>
+      <c r="J44" t="s">
+        <v>642</v>
       </c>
     </row>
   </sheetData>
@@ -6359,49 +8171,339 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>558</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>554</v>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" t="s">
+        <v>604</v>
+      </c>
+      <c r="G5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" t="s">
+        <v>582</v>
+      </c>
+      <c r="J5" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B6" t="s">
+        <v>580</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" t="s">
+        <v>415</v>
+      </c>
+      <c r="E6" t="s">
+        <v>413</v>
+      </c>
+      <c r="F6" t="s">
+        <v>644</v>
+      </c>
+      <c r="G6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" t="s">
+        <v>582</v>
+      </c>
+      <c r="J6" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>584</v>
+      </c>
+      <c r="B7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" t="s">
+        <v>604</v>
+      </c>
+      <c r="G7" t="s">
+        <v>182</v>
+      </c>
+      <c r="I7" t="s">
+        <v>582</v>
+      </c>
+      <c r="J7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>584</v>
+      </c>
+      <c r="B8" t="s">
+        <v>585</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F8" t="s">
+        <v>644</v>
+      </c>
+      <c r="G8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8" t="s">
+        <v>582</v>
+      </c>
+      <c r="J8" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>587</v>
+      </c>
+      <c r="B9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" t="s">
+        <v>604</v>
+      </c>
+      <c r="G9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I9" t="s">
+        <v>589</v>
+      </c>
+      <c r="J9" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B10" t="s">
+        <v>588</v>
+      </c>
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" t="s">
+        <v>415</v>
+      </c>
+      <c r="E10" t="s">
+        <v>413</v>
+      </c>
+      <c r="F10" t="s">
+        <v>644</v>
+      </c>
+      <c r="G10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10" t="s">
+        <v>589</v>
+      </c>
+      <c r="J10" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>645</v>
+      </c>
+      <c r="B11" t="s">
+        <v>646</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>414</v>
+      </c>
+      <c r="E11" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" t="s">
+        <v>604</v>
+      </c>
+      <c r="G11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I11" t="s">
+        <v>589</v>
+      </c>
+      <c r="J11" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B12" t="s">
+        <v>592</v>
+      </c>
+      <c r="C12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" t="s">
+        <v>589</v>
+      </c>
+      <c r="J12" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>591</v>
+      </c>
+      <c r="B13" t="s">
+        <v>592</v>
+      </c>
+      <c r="C13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" t="s">
+        <v>413</v>
+      </c>
+      <c r="F13" t="s">
+        <v>644</v>
+      </c>
+      <c r="G13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13" t="s">
+        <v>589</v>
+      </c>
+      <c r="J13" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>645</v>
+      </c>
+      <c r="B14" t="s">
+        <v>646</v>
+      </c>
+      <c r="C14" t="s">
+        <v>390</v>
+      </c>
+      <c r="D14" t="s">
+        <v>415</v>
+      </c>
+      <c r="E14" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" t="s">
+        <v>604</v>
+      </c>
+      <c r="G14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" t="s">
+        <v>594</v>
+      </c>
+      <c r="J14" t="s">
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -6416,22 +8518,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>559</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>560</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>561</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>562</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -6446,22 +8548,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>563</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>560</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>561</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>562</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -6476,7 +8578,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>564</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -6491,12 +8593,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>565</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -6506,12 +8608,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>562</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>566</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -6526,7 +8628,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>567</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -6541,7 +8643,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -6556,12 +8658,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>569</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -6571,7 +8673,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>566</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -6611,12 +8713,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6631,12 +8733,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -6651,7 +8753,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>572</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6666,127 +8768,127 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>573</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>574</v>
+        <v>664</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>575</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>576</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>577</v>
+        <v>667</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>578</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>579</v>
+        <v>669</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>580</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>581</v>
+        <v>671</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>582</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>583</v>
+        <v>673</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>584</v>
+        <v>674</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>585</v>
+        <v>675</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>586</v>
+        <v>676</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>587</v>
+        <v>677</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>588</v>
+        <v>678</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>589</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>590</v>
+        <v>680</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>591</v>
+        <v>681</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>592</v>
+        <v>682</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>593</v>
+        <v>683</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>594</v>
+        <v>684</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>595</v>
+        <v>685</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>596</v>
+        <v>686</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>597</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
